--- a/2026/GALERIA/Febrero/GALERIA Febrero.xlsx
+++ b/2026/GALERIA/Febrero/GALERIA Febrero.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2DC5AA-F8C4-4580-B222-2416A73D0CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E6C106-97DD-44E1-B706-014D7ECE3CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -945,9 +945,6 @@
     <t>VTO 13/03</t>
   </si>
   <si>
-    <t>CUIT DEL EDIFICIO: 30-66055743-8 - PERÍODO: FEBRERO - HORARIOS DE ATENCION: LUNES A VIERNES 10 A 16HS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mercantil andina seguro integral de consorcio - Poliza nro. 001166139 -  FEBRERO </t>
   </si>
   <si>
@@ -967,6 +964,9 @@
   </si>
   <si>
     <t>Transf 10/02</t>
+  </si>
+  <si>
+    <t>CUIT DEL EDIFICIO: 30-66055743-8 - PERÍODO: FEBRERO - HORARIOS DE ATENCION: LUNES A VIERNES 10 A 15HS</t>
   </si>
 </sst>
 </file>
@@ -2080,6 +2080,11 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2137,47 +2142,11 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2209,6 +2178,42 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2221,6 +2226,18 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2229,27 +2246,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2266,10 +2262,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2689,7 +2689,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="18"/>
@@ -2706,49 +2706,49 @@
       <c r="E6" s="22"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="226" t="s">
+      <c r="B8" s="229" t="s">
         <v>279</v>
       </c>
-      <c r="C8" s="226"/>
+      <c r="C8" s="229"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="226"/>
-      <c r="C9" s="226"/>
+      <c r="B9" s="229"/>
+      <c r="C9" s="229"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="226"/>
-      <c r="C10" s="226"/>
+      <c r="B10" s="229"/>
+      <c r="C10" s="229"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="234" t="s">
+      <c r="A13" s="237" t="s">
         <v>255</v>
       </c>
-      <c r="B13" s="234"/>
-      <c r="C13" s="234"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
+      <c r="B13" s="237"/>
+      <c r="C13" s="237"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="237"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="234"/>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
+      <c r="A14" s="237"/>
+      <c r="B14" s="237"/>
+      <c r="C14" s="237"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="237"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="234"/>
-      <c r="B15" s="234"/>
-      <c r="C15" s="234"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="234"/>
+      <c r="A15" s="237"/>
+      <c r="B15" s="237"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="237"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="234"/>
-      <c r="B16" s="234"/>
-      <c r="C16" s="234"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
+      <c r="A16" s="237"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -2775,10 +2775,10 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="227" t="s">
-        <v>284</v>
-      </c>
-      <c r="B22" s="235"/>
+      <c r="A22" s="230" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" s="238"/>
       <c r="C22" s="6"/>
       <c r="D22" s="207"/>
       <c r="E22" s="188" t="s">
@@ -2789,7 +2789,7 @@
     </row>
     <row r="23" spans="1:8" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="213" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B23" s="211"/>
       <c r="C23" s="6"/>
@@ -2824,10 +2824,10 @@
       <c r="E25" s="157"/>
     </row>
     <row r="26" spans="1:8" s="49" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="227" t="s">
-        <v>281</v>
-      </c>
-      <c r="B26" s="228"/>
+      <c r="A26" s="230" t="s">
+        <v>280</v>
+      </c>
+      <c r="B26" s="231"/>
       <c r="C26" s="185"/>
       <c r="D26" s="208">
         <v>111486</v>
@@ -2931,10 +2931,10 @@
       <c r="E35" s="147"/>
     </row>
     <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="227" t="s">
+      <c r="A36" s="230" t="s">
         <v>271</v>
       </c>
-      <c r="B36" s="228"/>
+      <c r="B36" s="231"/>
       <c r="C36" s="6"/>
       <c r="D36" s="172">
         <v>33150</v>
@@ -2942,27 +2942,27 @@
       <c r="E36" s="173"/>
     </row>
     <row r="37" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="290" t="s">
+      <c r="A37" s="228" t="s">
         <v>272</v>
       </c>
       <c r="B37" s="210"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="289">
+      <c r="D37" s="227">
         <v>60000</v>
       </c>
       <c r="E37" s="173"/>
     </row>
     <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="288">
+      <c r="D38" s="226">
         <v>77000</v>
       </c>
       <c r="E38" s="173" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J38" s="64"/>
     </row>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -3078,29 +3078,29 @@
       <c r="E50" s="168"/>
     </row>
     <row r="51" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="227"/>
-      <c r="B51" s="228"/>
+      <c r="A51" s="230"/>
+      <c r="B51" s="231"/>
       <c r="C51" s="6"/>
       <c r="D51" s="154"/>
       <c r="E51" s="146"/>
     </row>
     <row r="52" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="227"/>
-      <c r="B52" s="228"/>
+      <c r="A52" s="230"/>
+      <c r="B52" s="231"/>
       <c r="C52" s="6"/>
       <c r="D52" s="154"/>
       <c r="E52" s="146"/>
     </row>
     <row r="53" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="232"/>
-      <c r="B53" s="233"/>
+      <c r="A53" s="235"/>
+      <c r="B53" s="236"/>
       <c r="C53" s="6"/>
       <c r="D53" s="154"/>
       <c r="E53" s="146"/>
     </row>
     <row r="54" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="232"/>
-      <c r="B54" s="233"/>
+      <c r="A54" s="235"/>
+      <c r="B54" s="236"/>
       <c r="C54" s="64"/>
       <c r="D54" s="154"/>
       <c r="E54" s="146"/>
@@ -3185,51 +3185,51 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="231" t="s">
+      <c r="A69" s="234" t="s">
         <v>266</v>
       </c>
-      <c r="B69" s="231"/>
-      <c r="C69" s="231"/>
-      <c r="D69" s="231"/>
-      <c r="E69" s="231"/>
+      <c r="B69" s="234"/>
+      <c r="C69" s="234"/>
+      <c r="D69" s="234"/>
+      <c r="E69" s="234"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="231"/>
-      <c r="B70" s="231"/>
-      <c r="C70" s="231"/>
-      <c r="D70" s="231"/>
-      <c r="E70" s="231"/>
+      <c r="A70" s="234"/>
+      <c r="B70" s="234"/>
+      <c r="C70" s="234"/>
+      <c r="D70" s="234"/>
+      <c r="E70" s="234"/>
     </row>
     <row r="71" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="231"/>
-      <c r="B71" s="231"/>
-      <c r="C71" s="231"/>
-      <c r="D71" s="231"/>
-      <c r="E71" s="231"/>
+      <c r="A71" s="234"/>
+      <c r="B71" s="234"/>
+      <c r="C71" s="234"/>
+      <c r="D71" s="234"/>
+      <c r="E71" s="234"/>
     </row>
     <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="236" t="s">
+      <c r="A73" s="239" t="s">
         <v>273</v>
       </c>
-      <c r="B73" s="237"/>
-      <c r="C73" s="237"/>
-      <c r="D73" s="237"/>
-      <c r="E73" s="238"/>
+      <c r="B73" s="240"/>
+      <c r="C73" s="240"/>
+      <c r="D73" s="240"/>
+      <c r="E73" s="241"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="239"/>
-      <c r="B74" s="240"/>
-      <c r="C74" s="240"/>
-      <c r="D74" s="240"/>
-      <c r="E74" s="241"/>
+      <c r="A74" s="242"/>
+      <c r="B74" s="243"/>
+      <c r="C74" s="243"/>
+      <c r="D74" s="243"/>
+      <c r="E74" s="244"/>
     </row>
     <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="242"/>
-      <c r="B75" s="243"/>
-      <c r="C75" s="243"/>
-      <c r="D75" s="243"/>
-      <c r="E75" s="244"/>
+      <c r="A75" s="245"/>
+      <c r="B75" s="246"/>
+      <c r="C75" s="246"/>
+      <c r="D75" s="246"/>
+      <c r="E75" s="247"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="s">
@@ -3391,16 +3391,16 @@
     <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="95" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="230" t="s">
+      <c r="A96" s="233" t="s">
         <v>205</v>
       </c>
-      <c r="B96" s="230"/>
-      <c r="C96" s="230"/>
+      <c r="B96" s="233"/>
+      <c r="C96" s="233"/>
     </row>
     <row r="97" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="230"/>
-      <c r="B97" s="230"/>
-      <c r="C97" s="230"/>
+      <c r="A97" s="233"/>
+      <c r="B97" s="233"/>
+      <c r="C97" s="233"/>
     </row>
     <row r="98" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="170"/>
@@ -3433,32 +3433,32 @@
       <c r="M102" s="9"/>
     </row>
     <row r="103" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="229"/>
-      <c r="B103" s="229"/>
-      <c r="C103" s="229"/>
-      <c r="D103" s="229"/>
-      <c r="E103" s="229"/>
+      <c r="A103" s="232"/>
+      <c r="B103" s="232"/>
+      <c r="C103" s="232"/>
+      <c r="D103" s="232"/>
+      <c r="E103" s="232"/>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="229"/>
-      <c r="B104" s="229"/>
-      <c r="C104" s="229"/>
-      <c r="D104" s="229"/>
-      <c r="E104" s="229"/>
+      <c r="A104" s="232"/>
+      <c r="B104" s="232"/>
+      <c r="C104" s="232"/>
+      <c r="D104" s="232"/>
+      <c r="E104" s="232"/>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="229"/>
-      <c r="B105" s="229"/>
-      <c r="C105" s="229"/>
-      <c r="D105" s="229"/>
-      <c r="E105" s="229"/>
+      <c r="A105" s="232"/>
+      <c r="B105" s="232"/>
+      <c r="C105" s="232"/>
+      <c r="D105" s="232"/>
+      <c r="E105" s="232"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="229"/>
-      <c r="B106" s="229"/>
-      <c r="C106" s="229"/>
-      <c r="D106" s="229"/>
-      <c r="E106" s="229"/>
+      <c r="A106" s="232"/>
+      <c r="B106" s="232"/>
+      <c r="C106" s="232"/>
+      <c r="D106" s="232"/>
+      <c r="E106" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3496,28 +3496,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="277"/>
-      <c r="D2" s="277"/>
-      <c r="E2" s="277"/>
-      <c r="F2" s="277"/>
-      <c r="G2" s="277"/>
-      <c r="H2" s="278"/>
+      <c r="C2" s="289"/>
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
       <c r="I2" s="68"/>
       <c r="J2" s="69"/>
     </row>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="273" t="s">
+      <c r="B3" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="274"/>
-      <c r="D3" s="274"/>
-      <c r="E3" s="274"/>
-      <c r="F3" s="274"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="281"/>
+      <c r="E3" s="281"/>
+      <c r="F3" s="281"/>
+      <c r="G3" s="281"/>
+      <c r="H3" s="282"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
     </row>
@@ -3635,45 +3635,45 @@
       <c r="J14" s="81"/>
     </row>
     <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="281" t="s">
+      <c r="B15" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C15" s="282"/>
-      <c r="D15" s="282"/>
-      <c r="E15" s="282"/>
-      <c r="F15" s="282"/>
-      <c r="G15" s="279" t="e">
+      <c r="C15" s="277"/>
+      <c r="D15" s="277"/>
+      <c r="E15" s="277"/>
+      <c r="F15" s="277"/>
+      <c r="G15" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="280"/>
+      <c r="H15" s="279"/>
       <c r="I15" s="70"/>
       <c r="J15" s="80"/>
     </row>
     <row r="17" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="276" t="s">
+      <c r="B18" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C18" s="277"/>
-      <c r="D18" s="277"/>
-      <c r="E18" s="277"/>
-      <c r="F18" s="277"/>
-      <c r="G18" s="277"/>
-      <c r="H18" s="278"/>
+      <c r="C18" s="289"/>
+      <c r="D18" s="289"/>
+      <c r="E18" s="289"/>
+      <c r="F18" s="289"/>
+      <c r="G18" s="289"/>
+      <c r="H18" s="290"/>
       <c r="I18" s="68"/>
       <c r="J18" s="69"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="273" t="s">
+      <c r="B19" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="274"/>
-      <c r="D19" s="274"/>
-      <c r="E19" s="274"/>
-      <c r="F19" s="274"/>
-      <c r="G19" s="274"/>
-      <c r="H19" s="275"/>
+      <c r="C19" s="281"/>
+      <c r="D19" s="281"/>
+      <c r="E19" s="281"/>
+      <c r="F19" s="281"/>
+      <c r="G19" s="281"/>
+      <c r="H19" s="282"/>
       <c r="I19" s="1"/>
       <c r="J19" s="2"/>
     </row>
@@ -3791,46 +3791,46 @@
       <c r="J30" s="81"/>
     </row>
     <row r="31" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="281" t="s">
+      <c r="B31" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="282"/>
-      <c r="D31" s="282"/>
-      <c r="E31" s="282"/>
-      <c r="F31" s="282"/>
-      <c r="G31" s="279" t="e">
+      <c r="C31" s="277"/>
+      <c r="D31" s="277"/>
+      <c r="E31" s="277"/>
+      <c r="F31" s="277"/>
+      <c r="G31" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H31" s="280"/>
+      <c r="H31" s="279"/>
       <c r="I31" s="70"/>
       <c r="J31" s="80"/>
     </row>
     <row r="34" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="276" t="s">
+      <c r="B36" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="277"/>
-      <c r="D36" s="277"/>
-      <c r="E36" s="277"/>
-      <c r="F36" s="277"/>
-      <c r="G36" s="277"/>
-      <c r="H36" s="278"/>
+      <c r="C36" s="289"/>
+      <c r="D36" s="289"/>
+      <c r="E36" s="289"/>
+      <c r="F36" s="289"/>
+      <c r="G36" s="289"/>
+      <c r="H36" s="290"/>
       <c r="I36" s="68"/>
       <c r="J36" s="69"/>
     </row>
     <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="273" t="s">
+      <c r="B37" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="274"/>
-      <c r="D37" s="274"/>
-      <c r="E37" s="274"/>
-      <c r="F37" s="274"/>
-      <c r="G37" s="274"/>
-      <c r="H37" s="275"/>
+      <c r="C37" s="281"/>
+      <c r="D37" s="281"/>
+      <c r="E37" s="281"/>
+      <c r="F37" s="281"/>
+      <c r="G37" s="281"/>
+      <c r="H37" s="282"/>
       <c r="I37" s="1"/>
       <c r="J37" s="2"/>
     </row>
@@ -3948,45 +3948,45 @@
       <c r="J48" s="81"/>
     </row>
     <row r="49" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="281" t="s">
+      <c r="B49" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="282"/>
-      <c r="D49" s="282"/>
-      <c r="E49" s="282"/>
-      <c r="F49" s="282"/>
-      <c r="G49" s="279" t="e">
+      <c r="C49" s="277"/>
+      <c r="D49" s="277"/>
+      <c r="E49" s="277"/>
+      <c r="F49" s="277"/>
+      <c r="G49" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H49" s="280"/>
+      <c r="H49" s="279"/>
       <c r="I49" s="70"/>
       <c r="J49" s="80"/>
     </row>
     <row r="52" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="276" t="s">
+      <c r="B53" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C53" s="277"/>
-      <c r="D53" s="277"/>
-      <c r="E53" s="277"/>
-      <c r="F53" s="277"/>
-      <c r="G53" s="277"/>
-      <c r="H53" s="278"/>
+      <c r="C53" s="289"/>
+      <c r="D53" s="289"/>
+      <c r="E53" s="289"/>
+      <c r="F53" s="289"/>
+      <c r="G53" s="289"/>
+      <c r="H53" s="290"/>
       <c r="I53" s="68"/>
       <c r="J53" s="69"/>
     </row>
     <row r="54" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="273" t="s">
+      <c r="B54" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="274"/>
-      <c r="D54" s="274"/>
-      <c r="E54" s="274"/>
-      <c r="F54" s="274"/>
-      <c r="G54" s="274"/>
-      <c r="H54" s="275"/>
+      <c r="C54" s="281"/>
+      <c r="D54" s="281"/>
+      <c r="E54" s="281"/>
+      <c r="F54" s="281"/>
+      <c r="G54" s="281"/>
+      <c r="H54" s="282"/>
       <c r="I54" s="1"/>
       <c r="J54" s="2"/>
     </row>
@@ -4104,45 +4104,45 @@
       <c r="J65" s="81"/>
     </row>
     <row r="66" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="281" t="s">
+      <c r="B66" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="282"/>
-      <c r="D66" s="282"/>
-      <c r="E66" s="282"/>
-      <c r="F66" s="282"/>
-      <c r="G66" s="279" t="e">
+      <c r="C66" s="277"/>
+      <c r="D66" s="277"/>
+      <c r="E66" s="277"/>
+      <c r="F66" s="277"/>
+      <c r="G66" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H66" s="280"/>
+      <c r="H66" s="279"/>
       <c r="I66" s="70"/>
       <c r="J66" s="80"/>
     </row>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="71" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="276" t="s">
+      <c r="B71" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C71" s="277"/>
-      <c r="D71" s="277"/>
-      <c r="E71" s="277"/>
-      <c r="F71" s="277"/>
-      <c r="G71" s="277"/>
-      <c r="H71" s="278"/>
+      <c r="C71" s="289"/>
+      <c r="D71" s="289"/>
+      <c r="E71" s="289"/>
+      <c r="F71" s="289"/>
+      <c r="G71" s="289"/>
+      <c r="H71" s="290"/>
       <c r="I71" s="68"/>
       <c r="J71" s="69"/>
     </row>
     <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="273" t="s">
+      <c r="B72" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="274"/>
-      <c r="D72" s="274"/>
-      <c r="E72" s="274"/>
-      <c r="F72" s="274"/>
-      <c r="G72" s="274"/>
-      <c r="H72" s="275"/>
+      <c r="C72" s="281"/>
+      <c r="D72" s="281"/>
+      <c r="E72" s="281"/>
+      <c r="F72" s="281"/>
+      <c r="G72" s="281"/>
+      <c r="H72" s="282"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
     </row>
@@ -4260,18 +4260,18 @@
       <c r="J83" s="81"/>
     </row>
     <row r="84" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="281" t="s">
+      <c r="B84" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="282"/>
-      <c r="D84" s="282"/>
-      <c r="E84" s="282"/>
-      <c r="F84" s="282"/>
-      <c r="G84" s="279" t="e">
+      <c r="C84" s="277"/>
+      <c r="D84" s="277"/>
+      <c r="E84" s="277"/>
+      <c r="F84" s="277"/>
+      <c r="G84" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H84" s="280"/>
+      <c r="H84" s="279"/>
       <c r="I84" s="70"/>
       <c r="J84" s="80"/>
     </row>
@@ -4279,28 +4279,28 @@
     <row r="87" spans="2:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="88" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="89" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="276" t="s">
+      <c r="B89" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C89" s="277"/>
-      <c r="D89" s="277"/>
-      <c r="E89" s="277"/>
-      <c r="F89" s="277"/>
-      <c r="G89" s="277"/>
-      <c r="H89" s="278"/>
+      <c r="C89" s="289"/>
+      <c r="D89" s="289"/>
+      <c r="E89" s="289"/>
+      <c r="F89" s="289"/>
+      <c r="G89" s="289"/>
+      <c r="H89" s="290"/>
       <c r="I89" s="68"/>
       <c r="J89" s="69"/>
     </row>
     <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="273" t="s">
+      <c r="B90" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C90" s="274"/>
-      <c r="D90" s="274"/>
-      <c r="E90" s="274"/>
-      <c r="F90" s="274"/>
-      <c r="G90" s="274"/>
-      <c r="H90" s="275"/>
+      <c r="C90" s="281"/>
+      <c r="D90" s="281"/>
+      <c r="E90" s="281"/>
+      <c r="F90" s="281"/>
+      <c r="G90" s="281"/>
+      <c r="H90" s="282"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
     </row>
@@ -4418,45 +4418,45 @@
       <c r="J101" s="81"/>
     </row>
     <row r="102" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="281" t="s">
+      <c r="B102" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="282"/>
-      <c r="D102" s="282"/>
-      <c r="E102" s="282"/>
-      <c r="F102" s="282"/>
-      <c r="G102" s="279" t="e">
+      <c r="C102" s="277"/>
+      <c r="D102" s="277"/>
+      <c r="E102" s="277"/>
+      <c r="F102" s="277"/>
+      <c r="G102" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H102" s="280"/>
+      <c r="H102" s="279"/>
       <c r="I102" s="70"/>
       <c r="J102" s="80"/>
     </row>
     <row r="105" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="106" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="276" t="s">
+      <c r="B106" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C106" s="277"/>
-      <c r="D106" s="277"/>
-      <c r="E106" s="277"/>
-      <c r="F106" s="277"/>
-      <c r="G106" s="277"/>
-      <c r="H106" s="278"/>
+      <c r="C106" s="289"/>
+      <c r="D106" s="289"/>
+      <c r="E106" s="289"/>
+      <c r="F106" s="289"/>
+      <c r="G106" s="289"/>
+      <c r="H106" s="290"/>
       <c r="I106" s="68"/>
       <c r="J106" s="69"/>
     </row>
     <row r="107" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B107" s="273" t="s">
+      <c r="B107" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C107" s="274"/>
-      <c r="D107" s="274"/>
-      <c r="E107" s="274"/>
-      <c r="F107" s="274"/>
-      <c r="G107" s="274"/>
-      <c r="H107" s="275"/>
+      <c r="C107" s="281"/>
+      <c r="D107" s="281"/>
+      <c r="E107" s="281"/>
+      <c r="F107" s="281"/>
+      <c r="G107" s="281"/>
+      <c r="H107" s="282"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
     </row>
@@ -4574,46 +4574,46 @@
       <c r="J118" s="81"/>
     </row>
     <row r="119" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="281" t="s">
+      <c r="B119" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C119" s="282"/>
-      <c r="D119" s="282"/>
-      <c r="E119" s="282"/>
-      <c r="F119" s="282"/>
-      <c r="G119" s="279" t="e">
+      <c r="C119" s="277"/>
+      <c r="D119" s="277"/>
+      <c r="E119" s="277"/>
+      <c r="F119" s="277"/>
+      <c r="G119" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H119" s="280"/>
+      <c r="H119" s="279"/>
       <c r="I119" s="70"/>
       <c r="J119" s="80"/>
     </row>
     <row r="121" spans="2:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="122" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="123" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B123" s="276" t="s">
+      <c r="B123" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C123" s="277"/>
-      <c r="D123" s="277"/>
-      <c r="E123" s="277"/>
-      <c r="F123" s="277"/>
-      <c r="G123" s="277"/>
-      <c r="H123" s="278"/>
+      <c r="C123" s="289"/>
+      <c r="D123" s="289"/>
+      <c r="E123" s="289"/>
+      <c r="F123" s="289"/>
+      <c r="G123" s="289"/>
+      <c r="H123" s="290"/>
       <c r="I123" s="68"/>
       <c r="J123" s="69"/>
     </row>
     <row r="124" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="273" t="s">
+      <c r="B124" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C124" s="274"/>
-      <c r="D124" s="274"/>
-      <c r="E124" s="274"/>
-      <c r="F124" s="274"/>
-      <c r="G124" s="274"/>
-      <c r="H124" s="275"/>
+      <c r="C124" s="281"/>
+      <c r="D124" s="281"/>
+      <c r="E124" s="281"/>
+      <c r="F124" s="281"/>
+      <c r="G124" s="281"/>
+      <c r="H124" s="282"/>
       <c r="I124" s="1"/>
       <c r="J124" s="2"/>
     </row>
@@ -4731,45 +4731,45 @@
       <c r="J135" s="81"/>
     </row>
     <row r="136" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B136" s="281" t="s">
+      <c r="B136" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C136" s="282"/>
-      <c r="D136" s="282"/>
-      <c r="E136" s="282"/>
-      <c r="F136" s="282"/>
-      <c r="G136" s="279" t="e">
+      <c r="C136" s="277"/>
+      <c r="D136" s="277"/>
+      <c r="E136" s="277"/>
+      <c r="F136" s="277"/>
+      <c r="G136" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H136" s="280"/>
+      <c r="H136" s="279"/>
       <c r="I136" s="70"/>
       <c r="J136" s="80"/>
     </row>
     <row r="140" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="141" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="276" t="s">
+      <c r="B141" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C141" s="277"/>
-      <c r="D141" s="277"/>
-      <c r="E141" s="277"/>
-      <c r="F141" s="277"/>
-      <c r="G141" s="277"/>
-      <c r="H141" s="278"/>
+      <c r="C141" s="289"/>
+      <c r="D141" s="289"/>
+      <c r="E141" s="289"/>
+      <c r="F141" s="289"/>
+      <c r="G141" s="289"/>
+      <c r="H141" s="290"/>
       <c r="I141" s="68"/>
       <c r="J141" s="69"/>
     </row>
     <row r="142" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B142" s="273" t="s">
+      <c r="B142" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C142" s="274"/>
-      <c r="D142" s="274"/>
-      <c r="E142" s="274"/>
-      <c r="F142" s="274"/>
-      <c r="G142" s="274"/>
-      <c r="H142" s="275"/>
+      <c r="C142" s="281"/>
+      <c r="D142" s="281"/>
+      <c r="E142" s="281"/>
+      <c r="F142" s="281"/>
+      <c r="G142" s="281"/>
+      <c r="H142" s="282"/>
       <c r="I142" s="1"/>
       <c r="J142" s="2"/>
     </row>
@@ -4887,45 +4887,45 @@
       <c r="J153" s="81"/>
     </row>
     <row r="154" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B154" s="281" t="s">
+      <c r="B154" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C154" s="282"/>
-      <c r="D154" s="282"/>
-      <c r="E154" s="282"/>
-      <c r="F154" s="282"/>
-      <c r="G154" s="279" t="e">
+      <c r="C154" s="277"/>
+      <c r="D154" s="277"/>
+      <c r="E154" s="277"/>
+      <c r="F154" s="277"/>
+      <c r="G154" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H154" s="280"/>
+      <c r="H154" s="279"/>
       <c r="I154" s="70"/>
       <c r="J154" s="80"/>
     </row>
     <row r="157" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="158" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B158" s="276" t="s">
+      <c r="B158" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C158" s="277"/>
-      <c r="D158" s="277"/>
-      <c r="E158" s="277"/>
-      <c r="F158" s="277"/>
-      <c r="G158" s="277"/>
-      <c r="H158" s="278"/>
+      <c r="C158" s="289"/>
+      <c r="D158" s="289"/>
+      <c r="E158" s="289"/>
+      <c r="F158" s="289"/>
+      <c r="G158" s="289"/>
+      <c r="H158" s="290"/>
       <c r="I158" s="68"/>
       <c r="J158" s="69"/>
     </row>
     <row r="159" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B159" s="273" t="s">
+      <c r="B159" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C159" s="274"/>
-      <c r="D159" s="274"/>
-      <c r="E159" s="274"/>
-      <c r="F159" s="274"/>
-      <c r="G159" s="274"/>
-      <c r="H159" s="275"/>
+      <c r="C159" s="281"/>
+      <c r="D159" s="281"/>
+      <c r="E159" s="281"/>
+      <c r="F159" s="281"/>
+      <c r="G159" s="281"/>
+      <c r="H159" s="282"/>
       <c r="I159" s="1"/>
       <c r="J159" s="2"/>
     </row>
@@ -5043,56 +5043,44 @@
       <c r="J170" s="81"/>
     </row>
     <row r="171" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B171" s="281" t="s">
+      <c r="B171" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C171" s="282"/>
-      <c r="D171" s="282"/>
-      <c r="E171" s="282"/>
-      <c r="F171" s="282"/>
-      <c r="G171" s="279" t="e">
+      <c r="C171" s="277"/>
+      <c r="D171" s="277"/>
+      <c r="E171" s="277"/>
+      <c r="F171" s="277"/>
+      <c r="G171" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H171" s="280"/>
+      <c r="H171" s="279"/>
       <c r="I171" s="70"/>
       <c r="J171" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="B171:F171"/>
-    <mergeCell ref="G171:H171"/>
-    <mergeCell ref="B141:H141"/>
-    <mergeCell ref="B142:H142"/>
-    <mergeCell ref="B146:H146"/>
-    <mergeCell ref="B158:H158"/>
-    <mergeCell ref="B159:H159"/>
-    <mergeCell ref="B163:H163"/>
-    <mergeCell ref="B154:F154"/>
-    <mergeCell ref="G154:H154"/>
-    <mergeCell ref="I165:J165"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="G136:H136"/>
-    <mergeCell ref="B128:H128"/>
-    <mergeCell ref="I167:J167"/>
-    <mergeCell ref="I148:J148"/>
-    <mergeCell ref="I150:J150"/>
-    <mergeCell ref="B123:H123"/>
-    <mergeCell ref="B124:H124"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="G119:H119"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="B89:H89"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B94:H94"/>
-    <mergeCell ref="B106:H106"/>
-    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B54:H54"/>
@@ -5109,27 +5097,39 @@
     <mergeCell ref="I78:J78"/>
     <mergeCell ref="I80:J80"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B106:H106"/>
+    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B123:H123"/>
+    <mergeCell ref="B124:H124"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="I165:J165"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="B128:H128"/>
+    <mergeCell ref="I167:J167"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="I150:J150"/>
+    <mergeCell ref="B171:F171"/>
+    <mergeCell ref="G171:H171"/>
+    <mergeCell ref="B141:H141"/>
+    <mergeCell ref="B142:H142"/>
+    <mergeCell ref="B146:H146"/>
+    <mergeCell ref="B158:H158"/>
+    <mergeCell ref="B159:H159"/>
+    <mergeCell ref="B163:H163"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="G154:H154"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5151,28 +5151,28 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="276" t="s">
+      <c r="B4" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="277"/>
-      <c r="D4" s="277"/>
-      <c r="E4" s="277"/>
-      <c r="F4" s="277"/>
-      <c r="G4" s="277"/>
-      <c r="H4" s="278"/>
+      <c r="C4" s="289"/>
+      <c r="D4" s="289"/>
+      <c r="E4" s="289"/>
+      <c r="F4" s="289"/>
+      <c r="G4" s="289"/>
+      <c r="H4" s="290"/>
       <c r="I4" s="68"/>
       <c r="J4" s="69"/>
     </row>
     <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="273" t="s">
+      <c r="B5" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="274"/>
-      <c r="D5" s="274"/>
-      <c r="E5" s="274"/>
-      <c r="F5" s="274"/>
-      <c r="G5" s="274"/>
-      <c r="H5" s="275"/>
+      <c r="C5" s="281"/>
+      <c r="D5" s="281"/>
+      <c r="E5" s="281"/>
+      <c r="F5" s="281"/>
+      <c r="G5" s="281"/>
+      <c r="H5" s="282"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2"/>
     </row>
@@ -5290,45 +5290,45 @@
       <c r="J16" s="81"/>
     </row>
     <row r="17" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="281" t="s">
+      <c r="B17" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C17" s="282"/>
-      <c r="D17" s="282"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="282"/>
-      <c r="G17" s="279" t="e">
+      <c r="C17" s="277"/>
+      <c r="D17" s="277"/>
+      <c r="E17" s="277"/>
+      <c r="F17" s="277"/>
+      <c r="G17" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H17" s="280"/>
+      <c r="H17" s="279"/>
       <c r="I17" s="70"/>
       <c r="J17" s="80"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="276" t="s">
+      <c r="B20" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="278"/>
+      <c r="C20" s="289"/>
+      <c r="D20" s="289"/>
+      <c r="E20" s="289"/>
+      <c r="F20" s="289"/>
+      <c r="G20" s="289"/>
+      <c r="H20" s="290"/>
       <c r="I20" s="68"/>
       <c r="J20" s="69"/>
     </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="273" t="s">
+      <c r="B21" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="274"/>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="275"/>
+      <c r="C21" s="281"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="281"/>
+      <c r="H21" s="282"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
     </row>
@@ -5446,18 +5446,18 @@
       <c r="J32" s="81"/>
     </row>
     <row r="33" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="281" t="s">
+      <c r="B33" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="282"/>
-      <c r="D33" s="282"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="282"/>
-      <c r="G33" s="279" t="e">
+      <c r="C33" s="277"/>
+      <c r="D33" s="277"/>
+      <c r="E33" s="277"/>
+      <c r="F33" s="277"/>
+      <c r="G33" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H33" s="280"/>
+      <c r="H33" s="279"/>
       <c r="I33" s="70"/>
       <c r="J33" s="80"/>
     </row>
@@ -5465,28 +5465,28 @@
     <row r="35" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="276" t="s">
+      <c r="B37" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="277"/>
-      <c r="D37" s="277"/>
-      <c r="E37" s="277"/>
-      <c r="F37" s="277"/>
-      <c r="G37" s="277"/>
-      <c r="H37" s="278"/>
+      <c r="C37" s="289"/>
+      <c r="D37" s="289"/>
+      <c r="E37" s="289"/>
+      <c r="F37" s="289"/>
+      <c r="G37" s="289"/>
+      <c r="H37" s="290"/>
       <c r="I37" s="68"/>
       <c r="J37" s="69"/>
     </row>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="273" t="s">
+      <c r="B38" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="274"/>
-      <c r="D38" s="274"/>
-      <c r="E38" s="274"/>
-      <c r="F38" s="274"/>
-      <c r="G38" s="274"/>
-      <c r="H38" s="275"/>
+      <c r="C38" s="281"/>
+      <c r="D38" s="281"/>
+      <c r="E38" s="281"/>
+      <c r="F38" s="281"/>
+      <c r="G38" s="281"/>
+      <c r="H38" s="282"/>
       <c r="I38" s="1"/>
       <c r="J38" s="2"/>
     </row>
@@ -5604,45 +5604,45 @@
       <c r="J49" s="81"/>
     </row>
     <row r="50" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="281" t="s">
+      <c r="B50" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="282"/>
-      <c r="D50" s="282"/>
-      <c r="E50" s="282"/>
-      <c r="F50" s="282"/>
-      <c r="G50" s="279" t="e">
+      <c r="C50" s="277"/>
+      <c r="D50" s="277"/>
+      <c r="E50" s="277"/>
+      <c r="F50" s="277"/>
+      <c r="G50" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H50" s="280"/>
+      <c r="H50" s="279"/>
       <c r="I50" s="70"/>
       <c r="J50" s="80"/>
     </row>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="54" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="276" t="s">
+      <c r="B54" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C54" s="277"/>
-      <c r="D54" s="277"/>
-      <c r="E54" s="277"/>
-      <c r="F54" s="277"/>
-      <c r="G54" s="277"/>
-      <c r="H54" s="278"/>
+      <c r="C54" s="289"/>
+      <c r="D54" s="289"/>
+      <c r="E54" s="289"/>
+      <c r="F54" s="289"/>
+      <c r="G54" s="289"/>
+      <c r="H54" s="290"/>
       <c r="I54" s="68"/>
       <c r="J54" s="69"/>
     </row>
     <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="273" t="s">
+      <c r="B55" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="274"/>
-      <c r="D55" s="274"/>
-      <c r="E55" s="274"/>
-      <c r="F55" s="274"/>
-      <c r="G55" s="274"/>
-      <c r="H55" s="275"/>
+      <c r="C55" s="281"/>
+      <c r="D55" s="281"/>
+      <c r="E55" s="281"/>
+      <c r="F55" s="281"/>
+      <c r="G55" s="281"/>
+      <c r="H55" s="282"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
     </row>
@@ -5760,45 +5760,45 @@
       <c r="J66" s="81"/>
     </row>
     <row r="67" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="281" t="s">
+      <c r="B67" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="282"/>
-      <c r="D67" s="282"/>
-      <c r="E67" s="282"/>
-      <c r="F67" s="282"/>
-      <c r="G67" s="279" t="e">
+      <c r="C67" s="277"/>
+      <c r="D67" s="277"/>
+      <c r="E67" s="277"/>
+      <c r="F67" s="277"/>
+      <c r="G67" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H67" s="280"/>
+      <c r="H67" s="279"/>
       <c r="I67" s="70"/>
       <c r="J67" s="80"/>
     </row>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="71" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="276" t="s">
+      <c r="B71" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C71" s="277"/>
-      <c r="D71" s="277"/>
-      <c r="E71" s="277"/>
-      <c r="F71" s="277"/>
-      <c r="G71" s="277"/>
-      <c r="H71" s="278"/>
+      <c r="C71" s="289"/>
+      <c r="D71" s="289"/>
+      <c r="E71" s="289"/>
+      <c r="F71" s="289"/>
+      <c r="G71" s="289"/>
+      <c r="H71" s="290"/>
       <c r="I71" s="68"/>
       <c r="J71" s="69"/>
     </row>
     <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="273" t="s">
+      <c r="B72" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="274"/>
-      <c r="D72" s="274"/>
-      <c r="E72" s="274"/>
-      <c r="F72" s="274"/>
-      <c r="G72" s="274"/>
-      <c r="H72" s="275"/>
+      <c r="C72" s="281"/>
+      <c r="D72" s="281"/>
+      <c r="E72" s="281"/>
+      <c r="F72" s="281"/>
+      <c r="G72" s="281"/>
+      <c r="H72" s="282"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
     </row>
@@ -5916,46 +5916,46 @@
       <c r="J83" s="81"/>
     </row>
     <row r="84" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="281" t="s">
+      <c r="B84" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="282"/>
-      <c r="D84" s="282"/>
-      <c r="E84" s="282"/>
-      <c r="F84" s="282"/>
-      <c r="G84" s="279" t="e">
+      <c r="C84" s="277"/>
+      <c r="D84" s="277"/>
+      <c r="E84" s="277"/>
+      <c r="F84" s="277"/>
+      <c r="G84" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H84" s="280"/>
+      <c r="H84" s="279"/>
       <c r="I84" s="70"/>
       <c r="J84" s="80"/>
     </row>
     <row r="86" spans="2:10" ht="201" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="88" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="89" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="276" t="s">
+      <c r="B89" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C89" s="277"/>
-      <c r="D89" s="277"/>
-      <c r="E89" s="277"/>
-      <c r="F89" s="277"/>
-      <c r="G89" s="277"/>
-      <c r="H89" s="278"/>
+      <c r="C89" s="289"/>
+      <c r="D89" s="289"/>
+      <c r="E89" s="289"/>
+      <c r="F89" s="289"/>
+      <c r="G89" s="289"/>
+      <c r="H89" s="290"/>
       <c r="I89" s="68"/>
       <c r="J89" s="69"/>
     </row>
     <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="273" t="s">
+      <c r="B90" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C90" s="274"/>
-      <c r="D90" s="274"/>
-      <c r="E90" s="274"/>
-      <c r="F90" s="274"/>
-      <c r="G90" s="274"/>
-      <c r="H90" s="275"/>
+      <c r="C90" s="281"/>
+      <c r="D90" s="281"/>
+      <c r="E90" s="281"/>
+      <c r="F90" s="281"/>
+      <c r="G90" s="281"/>
+      <c r="H90" s="282"/>
       <c r="I90" s="1"/>
       <c r="J90" s="2"/>
     </row>
@@ -6073,45 +6073,45 @@
       <c r="J101" s="81"/>
     </row>
     <row r="102" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="281" t="s">
+      <c r="B102" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="282"/>
-      <c r="D102" s="282"/>
-      <c r="E102" s="282"/>
-      <c r="F102" s="282"/>
-      <c r="G102" s="279" t="e">
+      <c r="C102" s="277"/>
+      <c r="D102" s="277"/>
+      <c r="E102" s="277"/>
+      <c r="F102" s="277"/>
+      <c r="G102" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H102" s="280"/>
+      <c r="H102" s="279"/>
       <c r="I102" s="70"/>
       <c r="J102" s="80"/>
     </row>
     <row r="106" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B107" s="276" t="s">
+      <c r="B107" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C107" s="277"/>
-      <c r="D107" s="277"/>
-      <c r="E107" s="277"/>
-      <c r="F107" s="277"/>
-      <c r="G107" s="277"/>
-      <c r="H107" s="278"/>
+      <c r="C107" s="289"/>
+      <c r="D107" s="289"/>
+      <c r="E107" s="289"/>
+      <c r="F107" s="289"/>
+      <c r="G107" s="289"/>
+      <c r="H107" s="290"/>
       <c r="I107" s="68"/>
       <c r="J107" s="69"/>
     </row>
     <row r="108" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="273" t="s">
+      <c r="B108" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C108" s="274"/>
-      <c r="D108" s="274"/>
-      <c r="E108" s="274"/>
-      <c r="F108" s="274"/>
-      <c r="G108" s="274"/>
-      <c r="H108" s="275"/>
+      <c r="C108" s="281"/>
+      <c r="D108" s="281"/>
+      <c r="E108" s="281"/>
+      <c r="F108" s="281"/>
+      <c r="G108" s="281"/>
+      <c r="H108" s="282"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
     </row>
@@ -6229,18 +6229,18 @@
       <c r="J119" s="81"/>
     </row>
     <row r="120" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="281" t="s">
+      <c r="B120" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C120" s="282"/>
-      <c r="D120" s="282"/>
-      <c r="E120" s="282"/>
-      <c r="F120" s="282"/>
-      <c r="G120" s="279" t="e">
+      <c r="C120" s="277"/>
+      <c r="D120" s="277"/>
+      <c r="E120" s="277"/>
+      <c r="F120" s="277"/>
+      <c r="G120" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H120" s="280"/>
+      <c r="H120" s="279"/>
       <c r="I120" s="70"/>
       <c r="J120" s="80"/>
     </row>
@@ -6248,28 +6248,28 @@
     <row r="122" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="124" spans="2:10" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="125" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="276" t="s">
+      <c r="B125" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C125" s="277"/>
-      <c r="D125" s="277"/>
-      <c r="E125" s="277"/>
-      <c r="F125" s="277"/>
-      <c r="G125" s="277"/>
-      <c r="H125" s="278"/>
+      <c r="C125" s="289"/>
+      <c r="D125" s="289"/>
+      <c r="E125" s="289"/>
+      <c r="F125" s="289"/>
+      <c r="G125" s="289"/>
+      <c r="H125" s="290"/>
       <c r="I125" s="68"/>
       <c r="J125" s="69"/>
     </row>
     <row r="126" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="273" t="s">
+      <c r="B126" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C126" s="274"/>
-      <c r="D126" s="274"/>
-      <c r="E126" s="274"/>
-      <c r="F126" s="274"/>
-      <c r="G126" s="274"/>
-      <c r="H126" s="275"/>
+      <c r="C126" s="281"/>
+      <c r="D126" s="281"/>
+      <c r="E126" s="281"/>
+      <c r="F126" s="281"/>
+      <c r="G126" s="281"/>
+      <c r="H126" s="282"/>
       <c r="I126" s="1"/>
       <c r="J126" s="2"/>
     </row>
@@ -6387,45 +6387,45 @@
       <c r="J137" s="81"/>
     </row>
     <row r="138" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B138" s="281" t="s">
+      <c r="B138" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C138" s="282"/>
-      <c r="D138" s="282"/>
-      <c r="E138" s="282"/>
-      <c r="F138" s="282"/>
-      <c r="G138" s="279" t="e">
+      <c r="C138" s="277"/>
+      <c r="D138" s="277"/>
+      <c r="E138" s="277"/>
+      <c r="F138" s="277"/>
+      <c r="G138" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H138" s="280"/>
+      <c r="H138" s="279"/>
       <c r="I138" s="70"/>
       <c r="J138" s="80"/>
     </row>
     <row r="141" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="142" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B142" s="276" t="s">
+      <c r="B142" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C142" s="277"/>
-      <c r="D142" s="277"/>
-      <c r="E142" s="277"/>
-      <c r="F142" s="277"/>
-      <c r="G142" s="277"/>
-      <c r="H142" s="278"/>
+      <c r="C142" s="289"/>
+      <c r="D142" s="289"/>
+      <c r="E142" s="289"/>
+      <c r="F142" s="289"/>
+      <c r="G142" s="289"/>
+      <c r="H142" s="290"/>
       <c r="I142" s="68"/>
       <c r="J142" s="69"/>
     </row>
     <row r="143" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="273" t="s">
+      <c r="B143" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C143" s="274"/>
-      <c r="D143" s="274"/>
-      <c r="E143" s="274"/>
-      <c r="F143" s="274"/>
-      <c r="G143" s="274"/>
-      <c r="H143" s="275"/>
+      <c r="C143" s="281"/>
+      <c r="D143" s="281"/>
+      <c r="E143" s="281"/>
+      <c r="F143" s="281"/>
+      <c r="G143" s="281"/>
+      <c r="H143" s="282"/>
       <c r="I143" s="1"/>
       <c r="J143" s="2"/>
     </row>
@@ -6543,45 +6543,45 @@
       <c r="J154" s="81"/>
     </row>
     <row r="155" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B155" s="281" t="s">
+      <c r="B155" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C155" s="282"/>
-      <c r="D155" s="282"/>
-      <c r="E155" s="282"/>
-      <c r="F155" s="282"/>
-      <c r="G155" s="279" t="e">
+      <c r="C155" s="277"/>
+      <c r="D155" s="277"/>
+      <c r="E155" s="277"/>
+      <c r="F155" s="277"/>
+      <c r="G155" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H155" s="280"/>
+      <c r="H155" s="279"/>
       <c r="I155" s="70"/>
       <c r="J155" s="80"/>
     </row>
     <row r="159" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="160" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B160" s="276" t="s">
+      <c r="B160" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C160" s="277"/>
-      <c r="D160" s="277"/>
-      <c r="E160" s="277"/>
-      <c r="F160" s="277"/>
-      <c r="G160" s="277"/>
-      <c r="H160" s="278"/>
+      <c r="C160" s="289"/>
+      <c r="D160" s="289"/>
+      <c r="E160" s="289"/>
+      <c r="F160" s="289"/>
+      <c r="G160" s="289"/>
+      <c r="H160" s="290"/>
       <c r="I160" s="68"/>
       <c r="J160" s="69"/>
     </row>
     <row r="161" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B161" s="273" t="s">
+      <c r="B161" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C161" s="274"/>
-      <c r="D161" s="274"/>
-      <c r="E161" s="274"/>
-      <c r="F161" s="274"/>
-      <c r="G161" s="274"/>
-      <c r="H161" s="275"/>
+      <c r="C161" s="281"/>
+      <c r="D161" s="281"/>
+      <c r="E161" s="281"/>
+      <c r="F161" s="281"/>
+      <c r="G161" s="281"/>
+      <c r="H161" s="282"/>
       <c r="I161" s="1"/>
       <c r="J161" s="2"/>
     </row>
@@ -6699,56 +6699,44 @@
       <c r="J172" s="81"/>
     </row>
     <row r="173" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B173" s="281" t="s">
+      <c r="B173" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C173" s="282"/>
-      <c r="D173" s="282"/>
-      <c r="E173" s="282"/>
-      <c r="F173" s="282"/>
-      <c r="G173" s="279" t="e">
+      <c r="C173" s="277"/>
+      <c r="D173" s="277"/>
+      <c r="E173" s="277"/>
+      <c r="F173" s="277"/>
+      <c r="G173" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H173" s="280"/>
+      <c r="H173" s="279"/>
       <c r="I173" s="70"/>
       <c r="J173" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="G173:H173"/>
-    <mergeCell ref="B142:H142"/>
-    <mergeCell ref="B143:H143"/>
-    <mergeCell ref="B147:H147"/>
-    <mergeCell ref="B160:H160"/>
-    <mergeCell ref="B161:H161"/>
-    <mergeCell ref="B165:H165"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="I167:J167"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="G138:H138"/>
-    <mergeCell ref="B130:H130"/>
-    <mergeCell ref="I169:J169"/>
-    <mergeCell ref="I149:J149"/>
-    <mergeCell ref="I151:J151"/>
-    <mergeCell ref="B125:H125"/>
-    <mergeCell ref="B126:H126"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="B120:F120"/>
-    <mergeCell ref="G120:H120"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="B89:H89"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B94:H94"/>
-    <mergeCell ref="B107:H107"/>
-    <mergeCell ref="B108:H108"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B54:H54"/>
     <mergeCell ref="B55:H55"/>
@@ -6765,27 +6753,39 @@
     <mergeCell ref="I78:J78"/>
     <mergeCell ref="I80:J80"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B108:H108"/>
+    <mergeCell ref="B125:H125"/>
+    <mergeCell ref="B126:H126"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="I167:J167"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="B130:H130"/>
+    <mergeCell ref="I169:J169"/>
+    <mergeCell ref="I149:J149"/>
+    <mergeCell ref="I151:J151"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="B142:H142"/>
+    <mergeCell ref="B143:H143"/>
+    <mergeCell ref="B147:H147"/>
+    <mergeCell ref="B160:H160"/>
+    <mergeCell ref="B161:H161"/>
+    <mergeCell ref="B165:H165"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="G155:H155"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6808,28 +6808,28 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="278"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="290"/>
       <c r="I3" s="68"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
     </row>
@@ -6947,45 +6947,45 @@
       <c r="J15" s="81"/>
     </row>
     <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="279" t="e">
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H16" s="280"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="70"/>
       <c r="J16" s="80"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="276" t="s">
+      <c r="B20" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="278"/>
+      <c r="C20" s="289"/>
+      <c r="D20" s="289"/>
+      <c r="E20" s="289"/>
+      <c r="F20" s="289"/>
+      <c r="G20" s="289"/>
+      <c r="H20" s="290"/>
       <c r="I20" s="68"/>
       <c r="J20" s="69"/>
     </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="273" t="s">
+      <c r="B21" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="274"/>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="275"/>
+      <c r="C21" s="281"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="281"/>
+      <c r="H21" s="282"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
     </row>
@@ -7103,18 +7103,18 @@
       <c r="J32" s="81"/>
     </row>
     <row r="33" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="281" t="s">
+      <c r="B33" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="282"/>
-      <c r="D33" s="282"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="282"/>
-      <c r="G33" s="279" t="e">
+      <c r="C33" s="277"/>
+      <c r="D33" s="277"/>
+      <c r="E33" s="277"/>
+      <c r="F33" s="277"/>
+      <c r="G33" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H33" s="280"/>
+      <c r="H33" s="279"/>
       <c r="I33" s="70"/>
       <c r="J33" s="80"/>
     </row>
@@ -7122,28 +7122,28 @@
     <row r="36" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="276" t="s">
+      <c r="B38" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="277"/>
-      <c r="D38" s="277"/>
-      <c r="E38" s="277"/>
-      <c r="F38" s="277"/>
-      <c r="G38" s="277"/>
-      <c r="H38" s="278"/>
+      <c r="C38" s="289"/>
+      <c r="D38" s="289"/>
+      <c r="E38" s="289"/>
+      <c r="F38" s="289"/>
+      <c r="G38" s="289"/>
+      <c r="H38" s="290"/>
       <c r="I38" s="68"/>
       <c r="J38" s="69"/>
     </row>
     <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="273" t="s">
+      <c r="B39" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="274"/>
-      <c r="D39" s="274"/>
-      <c r="E39" s="274"/>
-      <c r="F39" s="274"/>
-      <c r="G39" s="274"/>
-      <c r="H39" s="275"/>
+      <c r="C39" s="281"/>
+      <c r="D39" s="281"/>
+      <c r="E39" s="281"/>
+      <c r="F39" s="281"/>
+      <c r="G39" s="281"/>
+      <c r="H39" s="282"/>
       <c r="I39" s="1"/>
       <c r="J39" s="2"/>
     </row>
@@ -7261,45 +7261,45 @@
       <c r="J50" s="81"/>
     </row>
     <row r="51" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="281" t="s">
+      <c r="B51" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="279" t="e">
+      <c r="C51" s="277"/>
+      <c r="D51" s="277"/>
+      <c r="E51" s="277"/>
+      <c r="F51" s="277"/>
+      <c r="G51" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H51" s="280"/>
+      <c r="H51" s="279"/>
       <c r="I51" s="70"/>
       <c r="J51" s="80"/>
     </row>
     <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="56" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="276" t="s">
+      <c r="B56" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C56" s="277"/>
-      <c r="D56" s="277"/>
-      <c r="E56" s="277"/>
-      <c r="F56" s="277"/>
-      <c r="G56" s="277"/>
-      <c r="H56" s="278"/>
+      <c r="C56" s="289"/>
+      <c r="D56" s="289"/>
+      <c r="E56" s="289"/>
+      <c r="F56" s="289"/>
+      <c r="G56" s="289"/>
+      <c r="H56" s="290"/>
       <c r="I56" s="68"/>
       <c r="J56" s="69"/>
     </row>
     <row r="57" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="273" t="s">
+      <c r="B57" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="274"/>
-      <c r="D57" s="274"/>
-      <c r="E57" s="274"/>
-      <c r="F57" s="274"/>
-      <c r="G57" s="274"/>
-      <c r="H57" s="275"/>
+      <c r="C57" s="281"/>
+      <c r="D57" s="281"/>
+      <c r="E57" s="281"/>
+      <c r="F57" s="281"/>
+      <c r="G57" s="281"/>
+      <c r="H57" s="282"/>
       <c r="I57" s="1"/>
       <c r="J57" s="2"/>
     </row>
@@ -7417,45 +7417,45 @@
       <c r="J68" s="81"/>
     </row>
     <row r="69" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="281" t="s">
+      <c r="B69" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C69" s="282"/>
-      <c r="D69" s="282"/>
-      <c r="E69" s="282"/>
-      <c r="F69" s="282"/>
-      <c r="G69" s="279" t="e">
+      <c r="C69" s="277"/>
+      <c r="D69" s="277"/>
+      <c r="E69" s="277"/>
+      <c r="F69" s="277"/>
+      <c r="G69" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H69" s="280"/>
+      <c r="H69" s="279"/>
       <c r="I69" s="70"/>
       <c r="J69" s="80"/>
     </row>
     <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="73" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="276" t="s">
+      <c r="B73" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C73" s="277"/>
-      <c r="D73" s="277"/>
-      <c r="E73" s="277"/>
-      <c r="F73" s="277"/>
-      <c r="G73" s="277"/>
-      <c r="H73" s="278"/>
+      <c r="C73" s="289"/>
+      <c r="D73" s="289"/>
+      <c r="E73" s="289"/>
+      <c r="F73" s="289"/>
+      <c r="G73" s="289"/>
+      <c r="H73" s="290"/>
       <c r="I73" s="68"/>
       <c r="J73" s="69"/>
     </row>
     <row r="74" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="273" t="s">
+      <c r="B74" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="274"/>
-      <c r="D74" s="274"/>
-      <c r="E74" s="274"/>
-      <c r="F74" s="274"/>
-      <c r="G74" s="274"/>
-      <c r="H74" s="275"/>
+      <c r="C74" s="281"/>
+      <c r="D74" s="281"/>
+      <c r="E74" s="281"/>
+      <c r="F74" s="281"/>
+      <c r="G74" s="281"/>
+      <c r="H74" s="282"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
     </row>
@@ -7573,18 +7573,18 @@
       <c r="J85" s="81"/>
     </row>
     <row r="86" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="281" t="s">
+      <c r="B86" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C86" s="282"/>
-      <c r="D86" s="282"/>
-      <c r="E86" s="282"/>
-      <c r="F86" s="282"/>
-      <c r="G86" s="279" t="e">
+      <c r="C86" s="277"/>
+      <c r="D86" s="277"/>
+      <c r="E86" s="277"/>
+      <c r="F86" s="277"/>
+      <c r="G86" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H86" s="280"/>
+      <c r="H86" s="279"/>
       <c r="I86" s="70"/>
       <c r="J86" s="80"/>
     </row>
@@ -7593,28 +7593,28 @@
     <row r="89" spans="2:10" ht="76.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="276" t="s">
+      <c r="B91" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C91" s="277"/>
-      <c r="D91" s="277"/>
-      <c r="E91" s="277"/>
-      <c r="F91" s="277"/>
-      <c r="G91" s="277"/>
-      <c r="H91" s="278"/>
+      <c r="C91" s="289"/>
+      <c r="D91" s="289"/>
+      <c r="E91" s="289"/>
+      <c r="F91" s="289"/>
+      <c r="G91" s="289"/>
+      <c r="H91" s="290"/>
       <c r="I91" s="68"/>
       <c r="J91" s="69"/>
     </row>
     <row r="92" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="273" t="s">
+      <c r="B92" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="274"/>
-      <c r="D92" s="274"/>
-      <c r="E92" s="274"/>
-      <c r="F92" s="274"/>
-      <c r="G92" s="274"/>
-      <c r="H92" s="275"/>
+      <c r="C92" s="281"/>
+      <c r="D92" s="281"/>
+      <c r="E92" s="281"/>
+      <c r="F92" s="281"/>
+      <c r="G92" s="281"/>
+      <c r="H92" s="282"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
     </row>
@@ -7732,45 +7732,45 @@
       <c r="J103" s="81"/>
     </row>
     <row r="104" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="281" t="s">
+      <c r="B104" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="282"/>
-      <c r="D104" s="282"/>
-      <c r="E104" s="282"/>
-      <c r="F104" s="282"/>
-      <c r="G104" s="279" t="e">
+      <c r="C104" s="277"/>
+      <c r="D104" s="277"/>
+      <c r="E104" s="277"/>
+      <c r="F104" s="277"/>
+      <c r="G104" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H104" s="280"/>
+      <c r="H104" s="279"/>
       <c r="I104" s="70"/>
       <c r="J104" s="80"/>
     </row>
     <row r="107" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="276" t="s">
+      <c r="B108" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C108" s="277"/>
-      <c r="D108" s="277"/>
-      <c r="E108" s="277"/>
-      <c r="F108" s="277"/>
-      <c r="G108" s="277"/>
-      <c r="H108" s="278"/>
+      <c r="C108" s="289"/>
+      <c r="D108" s="289"/>
+      <c r="E108" s="289"/>
+      <c r="F108" s="289"/>
+      <c r="G108" s="289"/>
+      <c r="H108" s="290"/>
       <c r="I108" s="68"/>
       <c r="J108" s="69"/>
     </row>
     <row r="109" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="273" t="s">
+      <c r="B109" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C109" s="274"/>
-      <c r="D109" s="274"/>
-      <c r="E109" s="274"/>
-      <c r="F109" s="274"/>
-      <c r="G109" s="274"/>
-      <c r="H109" s="275"/>
+      <c r="C109" s="281"/>
+      <c r="D109" s="281"/>
+      <c r="E109" s="281"/>
+      <c r="F109" s="281"/>
+      <c r="G109" s="281"/>
+      <c r="H109" s="282"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
     </row>
@@ -7888,45 +7888,45 @@
       <c r="J120" s="81"/>
     </row>
     <row r="121" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="281" t="s">
+      <c r="B121" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C121" s="282"/>
-      <c r="D121" s="282"/>
-      <c r="E121" s="282"/>
-      <c r="F121" s="282"/>
-      <c r="G121" s="279" t="e">
+      <c r="C121" s="277"/>
+      <c r="D121" s="277"/>
+      <c r="E121" s="277"/>
+      <c r="F121" s="277"/>
+      <c r="G121" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H121" s="280"/>
+      <c r="H121" s="279"/>
       <c r="I121" s="70"/>
       <c r="J121" s="80"/>
     </row>
     <row r="124" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="125" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="276" t="s">
+      <c r="B125" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C125" s="277"/>
-      <c r="D125" s="277"/>
-      <c r="E125" s="277"/>
-      <c r="F125" s="277"/>
-      <c r="G125" s="277"/>
-      <c r="H125" s="278"/>
+      <c r="C125" s="289"/>
+      <c r="D125" s="289"/>
+      <c r="E125" s="289"/>
+      <c r="F125" s="289"/>
+      <c r="G125" s="289"/>
+      <c r="H125" s="290"/>
       <c r="I125" s="68"/>
       <c r="J125" s="69"/>
     </row>
     <row r="126" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="273" t="s">
+      <c r="B126" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C126" s="274"/>
-      <c r="D126" s="274"/>
-      <c r="E126" s="274"/>
-      <c r="F126" s="274"/>
-      <c r="G126" s="274"/>
-      <c r="H126" s="275"/>
+      <c r="C126" s="281"/>
+      <c r="D126" s="281"/>
+      <c r="E126" s="281"/>
+      <c r="F126" s="281"/>
+      <c r="G126" s="281"/>
+      <c r="H126" s="282"/>
       <c r="I126" s="1"/>
       <c r="J126" s="2"/>
     </row>
@@ -8044,33 +8044,54 @@
       <c r="J137" s="81"/>
     </row>
     <row r="138" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B138" s="281" t="s">
+      <c r="B138" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C138" s="282"/>
-      <c r="D138" s="282"/>
-      <c r="E138" s="282"/>
-      <c r="F138" s="282"/>
-      <c r="G138" s="279" t="e">
+      <c r="C138" s="277"/>
+      <c r="D138" s="277"/>
+      <c r="E138" s="277"/>
+      <c r="F138" s="277"/>
+      <c r="G138" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H138" s="280"/>
+      <c r="H138" s="279"/>
       <c r="I138" s="70"/>
       <c r="J138" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="G138:H138"/>
-    <mergeCell ref="B108:H108"/>
-    <mergeCell ref="B109:H109"/>
-    <mergeCell ref="B113:H113"/>
-    <mergeCell ref="B125:H125"/>
-    <mergeCell ref="B126:H126"/>
-    <mergeCell ref="B130:H130"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B78:H78"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:H51"/>
     <mergeCell ref="I80:J80"/>
     <mergeCell ref="I82:J82"/>
     <mergeCell ref="I115:J115"/>
@@ -8086,37 +8107,16 @@
     <mergeCell ref="G104:H104"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B78:H78"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B73:H73"/>
-    <mergeCell ref="B74:H74"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="B108:H108"/>
+    <mergeCell ref="B109:H109"/>
+    <mergeCell ref="B113:H113"/>
+    <mergeCell ref="B125:H125"/>
+    <mergeCell ref="B126:H126"/>
+    <mergeCell ref="B130:H130"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8138,28 +8138,28 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="278"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="290"/>
       <c r="I3" s="68"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
     </row>
@@ -8277,45 +8277,45 @@
       <c r="J15" s="81"/>
     </row>
     <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="279" t="e">
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H16" s="280"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="70"/>
       <c r="J16" s="80"/>
     </row>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="276" t="s">
+      <c r="B21" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
-      <c r="E21" s="277"/>
-      <c r="F21" s="277"/>
-      <c r="G21" s="277"/>
-      <c r="H21" s="278"/>
+      <c r="C21" s="289"/>
+      <c r="D21" s="289"/>
+      <c r="E21" s="289"/>
+      <c r="F21" s="289"/>
+      <c r="G21" s="289"/>
+      <c r="H21" s="290"/>
       <c r="I21" s="68"/>
       <c r="J21" s="69"/>
     </row>
     <row r="22" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="273" t="s">
+      <c r="B22" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="274"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="275"/>
+      <c r="C22" s="281"/>
+      <c r="D22" s="281"/>
+      <c r="E22" s="281"/>
+      <c r="F22" s="281"/>
+      <c r="G22" s="281"/>
+      <c r="H22" s="282"/>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
     </row>
@@ -8433,46 +8433,46 @@
       <c r="J33" s="81"/>
     </row>
     <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="281" t="s">
+      <c r="B34" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="282"/>
-      <c r="D34" s="282"/>
-      <c r="E34" s="282"/>
-      <c r="F34" s="282"/>
-      <c r="G34" s="279" t="e">
+      <c r="C34" s="277"/>
+      <c r="D34" s="277"/>
+      <c r="E34" s="277"/>
+      <c r="F34" s="277"/>
+      <c r="G34" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H34" s="280"/>
+      <c r="H34" s="279"/>
       <c r="I34" s="70"/>
       <c r="J34" s="80"/>
     </row>
     <row r="36" spans="2:10" ht="295.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="276" t="s">
+      <c r="B38" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="277"/>
-      <c r="D38" s="277"/>
-      <c r="E38" s="277"/>
-      <c r="F38" s="277"/>
-      <c r="G38" s="277"/>
-      <c r="H38" s="278"/>
+      <c r="C38" s="289"/>
+      <c r="D38" s="289"/>
+      <c r="E38" s="289"/>
+      <c r="F38" s="289"/>
+      <c r="G38" s="289"/>
+      <c r="H38" s="290"/>
       <c r="I38" s="68"/>
       <c r="J38" s="69"/>
     </row>
     <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="273" t="s">
+      <c r="B39" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="274"/>
-      <c r="D39" s="274"/>
-      <c r="E39" s="274"/>
-      <c r="F39" s="274"/>
-      <c r="G39" s="274"/>
-      <c r="H39" s="275"/>
+      <c r="C39" s="281"/>
+      <c r="D39" s="281"/>
+      <c r="E39" s="281"/>
+      <c r="F39" s="281"/>
+      <c r="G39" s="281"/>
+      <c r="H39" s="282"/>
       <c r="I39" s="1"/>
       <c r="J39" s="2"/>
     </row>
@@ -8590,46 +8590,46 @@
       <c r="J50" s="81"/>
     </row>
     <row r="51" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="281" t="s">
+      <c r="B51" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="279" t="e">
+      <c r="C51" s="277"/>
+      <c r="D51" s="277"/>
+      <c r="E51" s="277"/>
+      <c r="F51" s="277"/>
+      <c r="G51" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H51" s="280"/>
+      <c r="H51" s="279"/>
       <c r="I51" s="70"/>
       <c r="J51" s="80"/>
     </row>
     <row r="52" spans="2:10" ht="1.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="54" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="276" t="s">
+      <c r="B54" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C54" s="277"/>
-      <c r="D54" s="277"/>
-      <c r="E54" s="277"/>
-      <c r="F54" s="277"/>
-      <c r="G54" s="277"/>
-      <c r="H54" s="278"/>
+      <c r="C54" s="289"/>
+      <c r="D54" s="289"/>
+      <c r="E54" s="289"/>
+      <c r="F54" s="289"/>
+      <c r="G54" s="289"/>
+      <c r="H54" s="290"/>
       <c r="I54" s="68"/>
       <c r="J54" s="69"/>
     </row>
     <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="273" t="s">
+      <c r="B55" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="274"/>
-      <c r="D55" s="274"/>
-      <c r="E55" s="274"/>
-      <c r="F55" s="274"/>
-      <c r="G55" s="274"/>
-      <c r="H55" s="275"/>
+      <c r="C55" s="281"/>
+      <c r="D55" s="281"/>
+      <c r="E55" s="281"/>
+      <c r="F55" s="281"/>
+      <c r="G55" s="281"/>
+      <c r="H55" s="282"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
     </row>
@@ -8747,45 +8747,45 @@
       <c r="J66" s="81"/>
     </row>
     <row r="67" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="281" t="s">
+      <c r="B67" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="282"/>
-      <c r="D67" s="282"/>
-      <c r="E67" s="282"/>
-      <c r="F67" s="282"/>
-      <c r="G67" s="279" t="e">
+      <c r="C67" s="277"/>
+      <c r="D67" s="277"/>
+      <c r="E67" s="277"/>
+      <c r="F67" s="277"/>
+      <c r="G67" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H67" s="280"/>
+      <c r="H67" s="279"/>
       <c r="I67" s="70"/>
       <c r="J67" s="80"/>
     </row>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="71" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="276" t="s">
+      <c r="B71" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C71" s="277"/>
-      <c r="D71" s="277"/>
-      <c r="E71" s="277"/>
-      <c r="F71" s="277"/>
-      <c r="G71" s="277"/>
-      <c r="H71" s="278"/>
+      <c r="C71" s="289"/>
+      <c r="D71" s="289"/>
+      <c r="E71" s="289"/>
+      <c r="F71" s="289"/>
+      <c r="G71" s="289"/>
+      <c r="H71" s="290"/>
       <c r="I71" s="68"/>
       <c r="J71" s="69"/>
     </row>
     <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="273" t="s">
+      <c r="B72" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="274"/>
-      <c r="D72" s="274"/>
-      <c r="E72" s="274"/>
-      <c r="F72" s="274"/>
-      <c r="G72" s="274"/>
-      <c r="H72" s="275"/>
+      <c r="C72" s="281"/>
+      <c r="D72" s="281"/>
+      <c r="E72" s="281"/>
+      <c r="F72" s="281"/>
+      <c r="G72" s="281"/>
+      <c r="H72" s="282"/>
       <c r="I72" s="1"/>
       <c r="J72" s="2"/>
     </row>
@@ -8903,45 +8903,45 @@
       <c r="J83" s="81"/>
     </row>
     <row r="84" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="281" t="s">
+      <c r="B84" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="282"/>
-      <c r="D84" s="282"/>
-      <c r="E84" s="282"/>
-      <c r="F84" s="282"/>
-      <c r="G84" s="279" t="e">
+      <c r="C84" s="277"/>
+      <c r="D84" s="277"/>
+      <c r="E84" s="277"/>
+      <c r="F84" s="277"/>
+      <c r="G84" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H84" s="280"/>
+      <c r="H84" s="279"/>
       <c r="I84" s="70"/>
       <c r="J84" s="80"/>
     </row>
     <row r="87" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="88" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="276" t="s">
+      <c r="B88" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C88" s="277"/>
-      <c r="D88" s="277"/>
-      <c r="E88" s="277"/>
-      <c r="F88" s="277"/>
-      <c r="G88" s="277"/>
-      <c r="H88" s="278"/>
+      <c r="C88" s="289"/>
+      <c r="D88" s="289"/>
+      <c r="E88" s="289"/>
+      <c r="F88" s="289"/>
+      <c r="G88" s="289"/>
+      <c r="H88" s="290"/>
       <c r="I88" s="68"/>
       <c r="J88" s="69"/>
     </row>
     <row r="89" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="273" t="s">
+      <c r="B89" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C89" s="274"/>
-      <c r="D89" s="274"/>
-      <c r="E89" s="274"/>
-      <c r="F89" s="274"/>
-      <c r="G89" s="274"/>
-      <c r="H89" s="275"/>
+      <c r="C89" s="281"/>
+      <c r="D89" s="281"/>
+      <c r="E89" s="281"/>
+      <c r="F89" s="281"/>
+      <c r="G89" s="281"/>
+      <c r="H89" s="282"/>
       <c r="I89" s="1"/>
       <c r="J89" s="2"/>
     </row>
@@ -9059,42 +9059,30 @@
       <c r="J100" s="81"/>
     </row>
     <row r="101" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="281" t="s">
+      <c r="B101" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C101" s="282"/>
-      <c r="D101" s="282"/>
-      <c r="E101" s="282"/>
-      <c r="F101" s="282"/>
-      <c r="G101" s="279" t="e">
+      <c r="C101" s="277"/>
+      <c r="D101" s="277"/>
+      <c r="E101" s="277"/>
+      <c r="F101" s="277"/>
+      <c r="G101" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H101" s="280"/>
+      <c r="H101" s="279"/>
       <c r="I101" s="70"/>
       <c r="J101" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="B71:H71"/>
-    <mergeCell ref="B72:H72"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="B89:H89"/>
-    <mergeCell ref="B93:H93"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B8:H8"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="G67:H67"/>
     <mergeCell ref="B16:F16"/>
@@ -9111,13 +9099,25 @@
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="I78:J78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9136,28 +9136,28 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="277"/>
-      <c r="D2" s="277"/>
-      <c r="E2" s="277"/>
-      <c r="F2" s="277"/>
-      <c r="G2" s="277"/>
-      <c r="H2" s="278"/>
+      <c r="C2" s="289"/>
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="290"/>
       <c r="I2" s="68"/>
       <c r="J2" s="69"/>
     </row>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="273" t="s">
+      <c r="B3" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="274"/>
-      <c r="D3" s="274"/>
-      <c r="E3" s="274"/>
-      <c r="F3" s="274"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="275"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="281"/>
+      <c r="E3" s="281"/>
+      <c r="F3" s="281"/>
+      <c r="G3" s="281"/>
+      <c r="H3" s="282"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
     </row>
@@ -9275,45 +9275,45 @@
       <c r="J14" s="81"/>
     </row>
     <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="281" t="s">
+      <c r="B15" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C15" s="282"/>
-      <c r="D15" s="282"/>
-      <c r="E15" s="282"/>
-      <c r="F15" s="282"/>
-      <c r="G15" s="279" t="e">
+      <c r="C15" s="277"/>
+      <c r="D15" s="277"/>
+      <c r="E15" s="277"/>
+      <c r="F15" s="277"/>
+      <c r="G15" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="280"/>
+      <c r="H15" s="279"/>
       <c r="I15" s="70"/>
       <c r="J15" s="80"/>
     </row>
     <row r="17" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="276" t="s">
+      <c r="B18" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C18" s="277"/>
-      <c r="D18" s="277"/>
-      <c r="E18" s="277"/>
-      <c r="F18" s="277"/>
-      <c r="G18" s="277"/>
-      <c r="H18" s="278"/>
+      <c r="C18" s="289"/>
+      <c r="D18" s="289"/>
+      <c r="E18" s="289"/>
+      <c r="F18" s="289"/>
+      <c r="G18" s="289"/>
+      <c r="H18" s="290"/>
       <c r="I18" s="68"/>
       <c r="J18" s="69"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="273" t="s">
+      <c r="B19" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="274"/>
-      <c r="D19" s="274"/>
-      <c r="E19" s="274"/>
-      <c r="F19" s="274"/>
-      <c r="G19" s="274"/>
-      <c r="H19" s="275"/>
+      <c r="C19" s="281"/>
+      <c r="D19" s="281"/>
+      <c r="E19" s="281"/>
+      <c r="F19" s="281"/>
+      <c r="G19" s="281"/>
+      <c r="H19" s="282"/>
       <c r="I19" s="1"/>
       <c r="J19" s="2"/>
     </row>
@@ -9431,45 +9431,45 @@
       <c r="J30" s="81"/>
     </row>
     <row r="31" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="281" t="s">
+      <c r="B31" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C31" s="282"/>
-      <c r="D31" s="282"/>
-      <c r="E31" s="282"/>
-      <c r="F31" s="282"/>
-      <c r="G31" s="279" t="e">
+      <c r="C31" s="277"/>
+      <c r="D31" s="277"/>
+      <c r="E31" s="277"/>
+      <c r="F31" s="277"/>
+      <c r="G31" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H31" s="280"/>
+      <c r="H31" s="279"/>
       <c r="I31" s="70"/>
       <c r="J31" s="80"/>
     </row>
     <row r="33" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="276" t="s">
+      <c r="B34" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="277"/>
-      <c r="D34" s="277"/>
-      <c r="E34" s="277"/>
-      <c r="F34" s="277"/>
-      <c r="G34" s="277"/>
-      <c r="H34" s="278"/>
+      <c r="C34" s="289"/>
+      <c r="D34" s="289"/>
+      <c r="E34" s="289"/>
+      <c r="F34" s="289"/>
+      <c r="G34" s="289"/>
+      <c r="H34" s="290"/>
       <c r="I34" s="68"/>
       <c r="J34" s="69"/>
     </row>
     <row r="35" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="273" t="s">
+      <c r="B35" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="274"/>
-      <c r="D35" s="274"/>
-      <c r="E35" s="274"/>
-      <c r="F35" s="274"/>
-      <c r="G35" s="274"/>
-      <c r="H35" s="275"/>
+      <c r="C35" s="281"/>
+      <c r="D35" s="281"/>
+      <c r="E35" s="281"/>
+      <c r="F35" s="281"/>
+      <c r="G35" s="281"/>
+      <c r="H35" s="282"/>
       <c r="I35" s="1"/>
       <c r="J35" s="2"/>
     </row>
@@ -9587,45 +9587,45 @@
       <c r="J46" s="81"/>
     </row>
     <row r="47" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="281" t="s">
+      <c r="B47" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="282"/>
-      <c r="D47" s="282"/>
-      <c r="E47" s="282"/>
-      <c r="F47" s="282"/>
-      <c r="G47" s="279" t="e">
+      <c r="C47" s="277"/>
+      <c r="D47" s="277"/>
+      <c r="E47" s="277"/>
+      <c r="F47" s="277"/>
+      <c r="G47" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H47" s="280"/>
+      <c r="H47" s="279"/>
       <c r="I47" s="70"/>
       <c r="J47" s="80"/>
     </row>
     <row r="51" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="276" t="s">
+      <c r="B52" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="277"/>
-      <c r="D52" s="277"/>
-      <c r="E52" s="277"/>
-      <c r="F52" s="277"/>
-      <c r="G52" s="277"/>
-      <c r="H52" s="278"/>
+      <c r="C52" s="289"/>
+      <c r="D52" s="289"/>
+      <c r="E52" s="289"/>
+      <c r="F52" s="289"/>
+      <c r="G52" s="289"/>
+      <c r="H52" s="290"/>
       <c r="I52" s="68"/>
       <c r="J52" s="69"/>
     </row>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="273" t="s">
+      <c r="B53" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="274"/>
-      <c r="D53" s="274"/>
-      <c r="E53" s="274"/>
-      <c r="F53" s="274"/>
-      <c r="G53" s="274"/>
-      <c r="H53" s="275"/>
+      <c r="C53" s="281"/>
+      <c r="D53" s="281"/>
+      <c r="E53" s="281"/>
+      <c r="F53" s="281"/>
+      <c r="G53" s="281"/>
+      <c r="H53" s="282"/>
       <c r="I53" s="1"/>
       <c r="J53" s="2"/>
     </row>
@@ -9743,45 +9743,45 @@
       <c r="J64" s="81"/>
     </row>
     <row r="65" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="281" t="s">
+      <c r="B65" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C65" s="282"/>
-      <c r="D65" s="282"/>
-      <c r="E65" s="282"/>
-      <c r="F65" s="282"/>
-      <c r="G65" s="279" t="e">
+      <c r="C65" s="277"/>
+      <c r="D65" s="277"/>
+      <c r="E65" s="277"/>
+      <c r="F65" s="277"/>
+      <c r="G65" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H65" s="280"/>
+      <c r="H65" s="279"/>
       <c r="I65" s="70"/>
       <c r="J65" s="80"/>
     </row>
     <row r="69" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="276" t="s">
+      <c r="B70" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C70" s="277"/>
-      <c r="D70" s="277"/>
-      <c r="E70" s="277"/>
-      <c r="F70" s="277"/>
-      <c r="G70" s="277"/>
-      <c r="H70" s="278"/>
+      <c r="C70" s="289"/>
+      <c r="D70" s="289"/>
+      <c r="E70" s="289"/>
+      <c r="F70" s="289"/>
+      <c r="G70" s="289"/>
+      <c r="H70" s="290"/>
       <c r="I70" s="68"/>
       <c r="J70" s="69"/>
     </row>
     <row r="71" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="273" t="s">
+      <c r="B71" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C71" s="274"/>
-      <c r="D71" s="274"/>
-      <c r="E71" s="274"/>
-      <c r="F71" s="274"/>
-      <c r="G71" s="274"/>
-      <c r="H71" s="275"/>
+      <c r="C71" s="281"/>
+      <c r="D71" s="281"/>
+      <c r="E71" s="281"/>
+      <c r="F71" s="281"/>
+      <c r="G71" s="281"/>
+      <c r="H71" s="282"/>
       <c r="I71" s="1"/>
       <c r="J71" s="2"/>
     </row>
@@ -9899,45 +9899,45 @@
       <c r="J82" s="81"/>
     </row>
     <row r="83" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="281" t="s">
+      <c r="B83" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C83" s="282"/>
-      <c r="D83" s="282"/>
-      <c r="E83" s="282"/>
-      <c r="F83" s="282"/>
-      <c r="G83" s="279" t="e">
+      <c r="C83" s="277"/>
+      <c r="D83" s="277"/>
+      <c r="E83" s="277"/>
+      <c r="F83" s="277"/>
+      <c r="G83" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H83" s="280"/>
+      <c r="H83" s="279"/>
       <c r="I83" s="70"/>
       <c r="J83" s="80"/>
     </row>
     <row r="86" spans="2:10" ht="228" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="87" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="276" t="s">
+      <c r="B87" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C87" s="277"/>
-      <c r="D87" s="277"/>
-      <c r="E87" s="277"/>
-      <c r="F87" s="277"/>
-      <c r="G87" s="277"/>
-      <c r="H87" s="278"/>
+      <c r="C87" s="289"/>
+      <c r="D87" s="289"/>
+      <c r="E87" s="289"/>
+      <c r="F87" s="289"/>
+      <c r="G87" s="289"/>
+      <c r="H87" s="290"/>
       <c r="I87" s="68"/>
       <c r="J87" s="69"/>
     </row>
     <row r="88" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="273" t="s">
+      <c r="B88" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C88" s="274"/>
-      <c r="D88" s="274"/>
-      <c r="E88" s="274"/>
-      <c r="F88" s="274"/>
-      <c r="G88" s="274"/>
-      <c r="H88" s="275"/>
+      <c r="C88" s="281"/>
+      <c r="D88" s="281"/>
+      <c r="E88" s="281"/>
+      <c r="F88" s="281"/>
+      <c r="G88" s="281"/>
+      <c r="H88" s="282"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
     </row>
@@ -10055,45 +10055,45 @@
       <c r="J99" s="81"/>
     </row>
     <row r="100" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="281" t="s">
+      <c r="B100" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C100" s="282"/>
-      <c r="D100" s="282"/>
-      <c r="E100" s="282"/>
-      <c r="F100" s="282"/>
-      <c r="G100" s="279" t="e">
+      <c r="C100" s="277"/>
+      <c r="D100" s="277"/>
+      <c r="E100" s="277"/>
+      <c r="F100" s="277"/>
+      <c r="G100" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H100" s="280"/>
+      <c r="H100" s="279"/>
       <c r="I100" s="70"/>
       <c r="J100" s="80"/>
     </row>
     <row r="103" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="104" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="276" t="s">
+      <c r="B104" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C104" s="277"/>
-      <c r="D104" s="277"/>
-      <c r="E104" s="277"/>
-      <c r="F104" s="277"/>
-      <c r="G104" s="277"/>
-      <c r="H104" s="278"/>
+      <c r="C104" s="289"/>
+      <c r="D104" s="289"/>
+      <c r="E104" s="289"/>
+      <c r="F104" s="289"/>
+      <c r="G104" s="289"/>
+      <c r="H104" s="290"/>
       <c r="I104" s="68"/>
       <c r="J104" s="69"/>
     </row>
     <row r="105" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B105" s="273" t="s">
+      <c r="B105" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C105" s="274"/>
-      <c r="D105" s="274"/>
-      <c r="E105" s="274"/>
-      <c r="F105" s="274"/>
-      <c r="G105" s="274"/>
-      <c r="H105" s="275"/>
+      <c r="C105" s="281"/>
+      <c r="D105" s="281"/>
+      <c r="E105" s="281"/>
+      <c r="F105" s="281"/>
+      <c r="G105" s="281"/>
+      <c r="H105" s="282"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
     </row>
@@ -10211,45 +10211,45 @@
       <c r="J116" s="81"/>
     </row>
     <row r="117" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="281" t="s">
+      <c r="B117" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C117" s="282"/>
-      <c r="D117" s="282"/>
-      <c r="E117" s="282"/>
-      <c r="F117" s="282"/>
-      <c r="G117" s="279" t="e">
+      <c r="C117" s="277"/>
+      <c r="D117" s="277"/>
+      <c r="E117" s="277"/>
+      <c r="F117" s="277"/>
+      <c r="G117" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H117" s="280"/>
+      <c r="H117" s="279"/>
       <c r="I117" s="70"/>
       <c r="J117" s="80"/>
     </row>
     <row r="120" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="121" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="276" t="s">
+      <c r="B121" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C121" s="277"/>
-      <c r="D121" s="277"/>
-      <c r="E121" s="277"/>
-      <c r="F121" s="277"/>
-      <c r="G121" s="277"/>
-      <c r="H121" s="278"/>
+      <c r="C121" s="289"/>
+      <c r="D121" s="289"/>
+      <c r="E121" s="289"/>
+      <c r="F121" s="289"/>
+      <c r="G121" s="289"/>
+      <c r="H121" s="290"/>
       <c r="I121" s="68"/>
       <c r="J121" s="69"/>
     </row>
     <row r="122" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B122" s="273" t="s">
+      <c r="B122" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C122" s="274"/>
-      <c r="D122" s="274"/>
-      <c r="E122" s="274"/>
-      <c r="F122" s="274"/>
-      <c r="G122" s="274"/>
-      <c r="H122" s="275"/>
+      <c r="C122" s="281"/>
+      <c r="D122" s="281"/>
+      <c r="E122" s="281"/>
+      <c r="F122" s="281"/>
+      <c r="G122" s="281"/>
+      <c r="H122" s="282"/>
       <c r="I122" s="1"/>
       <c r="J122" s="2"/>
     </row>
@@ -10367,45 +10367,45 @@
       <c r="J133" s="81"/>
     </row>
     <row r="134" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B134" s="281" t="s">
+      <c r="B134" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C134" s="282"/>
-      <c r="D134" s="282"/>
-      <c r="E134" s="282"/>
-      <c r="F134" s="282"/>
-      <c r="G134" s="279" t="e">
+      <c r="C134" s="277"/>
+      <c r="D134" s="277"/>
+      <c r="E134" s="277"/>
+      <c r="F134" s="277"/>
+      <c r="G134" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H134" s="280"/>
+      <c r="H134" s="279"/>
       <c r="I134" s="70"/>
       <c r="J134" s="80"/>
     </row>
     <row r="138" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="139" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B139" s="276" t="s">
+      <c r="B139" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C139" s="277"/>
-      <c r="D139" s="277"/>
-      <c r="E139" s="277"/>
-      <c r="F139" s="277"/>
-      <c r="G139" s="277"/>
-      <c r="H139" s="278"/>
+      <c r="C139" s="289"/>
+      <c r="D139" s="289"/>
+      <c r="E139" s="289"/>
+      <c r="F139" s="289"/>
+      <c r="G139" s="289"/>
+      <c r="H139" s="290"/>
       <c r="I139" s="68"/>
       <c r="J139" s="69"/>
     </row>
     <row r="140" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="273" t="s">
+      <c r="B140" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C140" s="274"/>
-      <c r="D140" s="274"/>
-      <c r="E140" s="274"/>
-      <c r="F140" s="274"/>
-      <c r="G140" s="274"/>
-      <c r="H140" s="275"/>
+      <c r="C140" s="281"/>
+      <c r="D140" s="281"/>
+      <c r="E140" s="281"/>
+      <c r="F140" s="281"/>
+      <c r="G140" s="281"/>
+      <c r="H140" s="282"/>
       <c r="I140" s="1"/>
       <c r="J140" s="2"/>
     </row>
@@ -10523,55 +10523,38 @@
       <c r="J151" s="81"/>
     </row>
     <row r="152" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="281" t="s">
+      <c r="B152" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C152" s="282"/>
-      <c r="D152" s="282"/>
-      <c r="E152" s="282"/>
-      <c r="F152" s="282"/>
-      <c r="G152" s="279" t="e">
+      <c r="C152" s="277"/>
+      <c r="D152" s="277"/>
+      <c r="E152" s="277"/>
+      <c r="F152" s="277"/>
+      <c r="G152" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H152" s="280"/>
+      <c r="H152" s="279"/>
       <c r="I152" s="70"/>
       <c r="J152" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="I146:J146"/>
-    <mergeCell ref="I148:J148"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="G152:H152"/>
-    <mergeCell ref="B121:H121"/>
-    <mergeCell ref="B122:H122"/>
-    <mergeCell ref="B126:H126"/>
-    <mergeCell ref="B139:H139"/>
-    <mergeCell ref="B140:H140"/>
-    <mergeCell ref="B144:H144"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="G134:H134"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="B117:F117"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="B104:H104"/>
-    <mergeCell ref="B105:H105"/>
-    <mergeCell ref="B109:H109"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="B70:H70"/>
-    <mergeCell ref="B71:H71"/>
-    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="B92:H92"/>
@@ -10588,21 +10571,38 @@
     <mergeCell ref="I61:J61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="G65:H65"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B117:F117"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="B104:H104"/>
+    <mergeCell ref="B105:H105"/>
+    <mergeCell ref="B109:H109"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="I146:J146"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="G152:H152"/>
+    <mergeCell ref="B121:H121"/>
+    <mergeCell ref="B122:H122"/>
+    <mergeCell ref="B126:H126"/>
+    <mergeCell ref="B139:H139"/>
+    <mergeCell ref="B140:H140"/>
+    <mergeCell ref="B144:H144"/>
+    <mergeCell ref="I130:J130"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="G134:H134"/>
+    <mergeCell ref="I128:J128"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10636,12 +10636,12 @@
     <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
-      <c r="C1" s="245" t="s">
+      <c r="C1" s="261" t="s">
         <v>251</v>
       </c>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
@@ -10656,10 +10656,10 @@
     <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="246"/>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
+      <c r="C2" s="262"/>
+      <c r="D2" s="262"/>
+      <c r="E2" s="262"/>
+      <c r="F2" s="262"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
@@ -10674,10 +10674,10 @@
     <row r="3" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="246"/>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
+      <c r="C3" s="262"/>
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -10685,10 +10685,10 @@
         <v>252</v>
       </c>
       <c r="K3" s="7"/>
-      <c r="L3" s="247">
+      <c r="L3" s="263">
         <v>3200000</v>
       </c>
-      <c r="M3" s="247"/>
+      <c r="M3" s="263"/>
       <c r="N3" s="66"/>
       <c r="O3" s="66"/>
       <c r="P3" s="23"/>
@@ -10696,10 +10696,10 @@
     <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="246"/>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
@@ -10707,97 +10707,97 @@
         <v>252</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="248"/>
-      <c r="M4" s="248"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="264"/>
       <c r="N4" s="84"/>
       <c r="O4" s="84"/>
     </row>
     <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="267" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="254"/>
-      <c r="C5" s="254"/>
-      <c r="D5" s="254"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="254"/>
-      <c r="G5" s="254"/>
-      <c r="H5" s="254"/>
-      <c r="I5" s="254"/>
-      <c r="J5" s="254"/>
-      <c r="K5" s="254"/>
-      <c r="L5" s="254"/>
-      <c r="M5" s="254"/>
-      <c r="N5" s="254"/>
-      <c r="O5" s="255"/>
+      <c r="B5" s="268"/>
+      <c r="C5" s="268"/>
+      <c r="D5" s="268"/>
+      <c r="E5" s="268"/>
+      <c r="F5" s="268"/>
+      <c r="G5" s="268"/>
+      <c r="H5" s="268"/>
+      <c r="I5" s="268"/>
+      <c r="J5" s="268"/>
+      <c r="K5" s="268"/>
+      <c r="L5" s="268"/>
+      <c r="M5" s="268"/>
+      <c r="N5" s="268"/>
+      <c r="O5" s="269"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="249" t="s">
+      <c r="A6" s="265" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="251" t="s">
+      <c r="B6" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="251" t="s">
+      <c r="C6" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="251" t="s">
+      <c r="D6" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="E6" s="251" t="s">
+      <c r="E6" s="249" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="251" t="s">
+      <c r="F6" s="249" t="s">
         <v>225</v>
       </c>
-      <c r="G6" s="251" t="s">
+      <c r="G6" s="249" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="267" t="s">
+      <c r="H6" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="I6" s="267" t="s">
+      <c r="I6" s="258" t="s">
         <v>259</v>
       </c>
-      <c r="J6" s="262" t="s">
+      <c r="J6" s="253" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="262" t="s">
+      <c r="K6" s="253" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="265" t="s">
+      <c r="L6" s="256" t="s">
         <v>220</v>
       </c>
       <c r="M6" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="N6" s="260" t="s">
+      <c r="N6" s="251" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="256" t="s">
+      <c r="O6" s="270" t="s">
         <v>218</v>
       </c>
       <c r="R6" s="55"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="250"/>
-      <c r="B7" s="252"/>
-      <c r="C7" s="252"/>
-      <c r="D7" s="259"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="252"/>
-      <c r="G7" s="252"/>
-      <c r="H7" s="268"/>
-      <c r="I7" s="268"/>
-      <c r="J7" s="263"/>
-      <c r="K7" s="264"/>
-      <c r="L7" s="266"/>
+      <c r="A7" s="266"/>
+      <c r="B7" s="260"/>
+      <c r="C7" s="260"/>
+      <c r="D7" s="250"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="260"/>
+      <c r="G7" s="260"/>
+      <c r="H7" s="259"/>
+      <c r="I7" s="259"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="255"/>
+      <c r="L7" s="257"/>
       <c r="M7" s="85" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="N7" s="261"/>
-      <c r="O7" s="257"/>
+      <c r="N7" s="252"/>
+      <c r="O7" s="271"/>
     </row>
     <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
@@ -12351,96 +12351,87 @@
     </row>
     <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="258" t="s">
+      <c r="C38" s="248" t="s">
         <v>263</v>
       </c>
-      <c r="D38" s="258"/>
-      <c r="E38" s="258"/>
-      <c r="F38" s="258"/>
-      <c r="G38" s="258"/>
-      <c r="H38" s="258"/>
-      <c r="I38" s="258"/>
-      <c r="J38" s="258"/>
-      <c r="K38" s="258"/>
-      <c r="L38" s="258"/>
-      <c r="M38" s="258"/>
+      <c r="D38" s="248"/>
+      <c r="E38" s="248"/>
+      <c r="F38" s="248"/>
+      <c r="G38" s="248"/>
+      <c r="H38" s="248"/>
+      <c r="I38" s="248"/>
+      <c r="J38" s="248"/>
+      <c r="K38" s="248"/>
+      <c r="L38" s="248"/>
+      <c r="M38" s="248"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="258"/>
-      <c r="D39" s="258"/>
-      <c r="E39" s="258"/>
-      <c r="F39" s="258"/>
-      <c r="G39" s="258"/>
-      <c r="H39" s="258"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
-      <c r="M39" s="258"/>
+      <c r="C39" s="248"/>
+      <c r="D39" s="248"/>
+      <c r="E39" s="248"/>
+      <c r="F39" s="248"/>
+      <c r="G39" s="248"/>
+      <c r="H39" s="248"/>
+      <c r="I39" s="248"/>
+      <c r="J39" s="248"/>
+      <c r="K39" s="248"/>
+      <c r="L39" s="248"/>
+      <c r="M39" s="248"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="258"/>
-      <c r="D40" s="258"/>
-      <c r="E40" s="258"/>
-      <c r="F40" s="258"/>
-      <c r="G40" s="258"/>
-      <c r="H40" s="258"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
-      <c r="M40" s="258"/>
+      <c r="C40" s="248"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
+      <c r="I40" s="248"/>
+      <c r="J40" s="248"/>
+      <c r="K40" s="248"/>
+      <c r="L40" s="248"/>
+      <c r="M40" s="248"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="258"/>
-      <c r="D41" s="258"/>
-      <c r="E41" s="258"/>
-      <c r="F41" s="258"/>
-      <c r="G41" s="258"/>
-      <c r="H41" s="258"/>
-      <c r="I41" s="258"/>
-      <c r="J41" s="258"/>
-      <c r="K41" s="258"/>
-      <c r="L41" s="258"/>
-      <c r="M41" s="258"/>
+      <c r="C41" s="248"/>
+      <c r="D41" s="248"/>
+      <c r="E41" s="248"/>
+      <c r="F41" s="248"/>
+      <c r="G41" s="248"/>
+      <c r="H41" s="248"/>
+      <c r="I41" s="248"/>
+      <c r="J41" s="248"/>
+      <c r="K41" s="248"/>
+      <c r="L41" s="248"/>
+      <c r="M41" s="248"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="258"/>
-      <c r="D42" s="258"/>
-      <c r="E42" s="258"/>
-      <c r="F42" s="258"/>
-      <c r="G42" s="258"/>
-      <c r="H42" s="258"/>
-      <c r="I42" s="258"/>
-      <c r="J42" s="258"/>
-      <c r="K42" s="258"/>
-      <c r="L42" s="258"/>
-      <c r="M42" s="258"/>
+      <c r="C42" s="248"/>
+      <c r="D42" s="248"/>
+      <c r="E42" s="248"/>
+      <c r="F42" s="248"/>
+      <c r="G42" s="248"/>
+      <c r="H42" s="248"/>
+      <c r="I42" s="248"/>
+      <c r="J42" s="248"/>
+      <c r="K42" s="248"/>
+      <c r="L42" s="248"/>
+      <c r="M42" s="248"/>
     </row>
     <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="258"/>
-      <c r="D43" s="258"/>
-      <c r="E43" s="258"/>
-      <c r="F43" s="258"/>
-      <c r="G43" s="258"/>
-      <c r="H43" s="258"/>
-      <c r="I43" s="258"/>
-      <c r="J43" s="258"/>
-      <c r="K43" s="258"/>
-      <c r="L43" s="258"/>
-      <c r="M43" s="258"/>
+      <c r="C43" s="248"/>
+      <c r="D43" s="248"/>
+      <c r="E43" s="248"/>
+      <c r="F43" s="248"/>
+      <c r="G43" s="248"/>
+      <c r="H43" s="248"/>
+      <c r="I43" s="248"/>
+      <c r="J43" s="248"/>
+      <c r="K43" s="248"/>
+      <c r="L43" s="248"/>
+      <c r="M43" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -12451,6 +12442,15 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -12553,79 +12553,79 @@
       <c r="Q3" s="84"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="249" t="s">
+      <c r="A4" s="265" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="269" t="s">
+      <c r="B4" s="272" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="251" t="s">
+      <c r="D4" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="251" t="s">
+      <c r="E4" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="251" t="s">
+      <c r="F4" s="249" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="251" t="s">
+      <c r="G4" s="249" t="s">
         <v>226</v>
       </c>
-      <c r="H4" s="251" t="s">
+      <c r="H4" s="249" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="251" t="s">
+      <c r="I4" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="267" t="s">
+      <c r="J4" s="258" t="s">
         <v>126</v>
       </c>
-      <c r="K4" s="262" t="s">
+      <c r="K4" s="253" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="262" t="s">
+      <c r="L4" s="253" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="262" t="s">
+      <c r="M4" s="253" t="s">
         <v>222</v>
       </c>
-      <c r="N4" s="265" t="s">
+      <c r="N4" s="256" t="s">
         <v>220</v>
       </c>
       <c r="O4" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="P4" s="260" t="s">
+      <c r="P4" s="251" t="s">
         <v>46</v>
       </c>
-      <c r="Q4" s="256" t="s">
+      <c r="Q4" s="270" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="250"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="252"/>
-      <c r="D5" s="252"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="263"/>
-      <c r="M5" s="264"/>
-      <c r="N5" s="266"/>
+      <c r="A5" s="266"/>
+      <c r="B5" s="273"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="254"/>
+      <c r="M5" s="255"/>
+      <c r="N5" s="257"/>
       <c r="O5" s="85" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="261"/>
-      <c r="Q5" s="257"/>
+      <c r="P5" s="252"/>
+      <c r="Q5" s="271"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -17106,91 +17106,98 @@
     </row>
     <row r="83" spans="2:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="2:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D84" s="229"/>
-      <c r="E84" s="229"/>
-      <c r="F84" s="229"/>
-      <c r="G84" s="229"/>
-      <c r="H84" s="229"/>
-      <c r="I84" s="229"/>
-      <c r="J84" s="229"/>
-      <c r="K84" s="229"/>
-      <c r="L84" s="229"/>
-      <c r="M84" s="229"/>
-      <c r="N84" s="229"/>
-      <c r="O84" s="229"/>
+      <c r="D84" s="232"/>
+      <c r="E84" s="232"/>
+      <c r="F84" s="232"/>
+      <c r="G84" s="232"/>
+      <c r="H84" s="232"/>
+      <c r="I84" s="232"/>
+      <c r="J84" s="232"/>
+      <c r="K84" s="232"/>
+      <c r="L84" s="232"/>
+      <c r="M84" s="232"/>
+      <c r="N84" s="232"/>
+      <c r="O84" s="232"/>
     </row>
     <row r="85" spans="2:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="229"/>
-      <c r="E85" s="229"/>
-      <c r="F85" s="229"/>
-      <c r="G85" s="229"/>
-      <c r="H85" s="229"/>
-      <c r="I85" s="229"/>
-      <c r="J85" s="229"/>
-      <c r="K85" s="229"/>
-      <c r="L85" s="229"/>
-      <c r="M85" s="229"/>
-      <c r="N85" s="229"/>
-      <c r="O85" s="229"/>
+      <c r="D85" s="232"/>
+      <c r="E85" s="232"/>
+      <c r="F85" s="232"/>
+      <c r="G85" s="232"/>
+      <c r="H85" s="232"/>
+      <c r="I85" s="232"/>
+      <c r="J85" s="232"/>
+      <c r="K85" s="232"/>
+      <c r="L85" s="232"/>
+      <c r="M85" s="232"/>
+      <c r="N85" s="232"/>
+      <c r="O85" s="232"/>
     </row>
     <row r="86" spans="2:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="229"/>
-      <c r="E86" s="229"/>
-      <c r="F86" s="229"/>
-      <c r="G86" s="229"/>
-      <c r="H86" s="229"/>
-      <c r="I86" s="229"/>
-      <c r="J86" s="229"/>
-      <c r="K86" s="229"/>
-      <c r="L86" s="229"/>
-      <c r="M86" s="229"/>
-      <c r="N86" s="229"/>
-      <c r="O86" s="229"/>
+      <c r="D86" s="232"/>
+      <c r="E86" s="232"/>
+      <c r="F86" s="232"/>
+      <c r="G86" s="232"/>
+      <c r="H86" s="232"/>
+      <c r="I86" s="232"/>
+      <c r="J86" s="232"/>
+      <c r="K86" s="232"/>
+      <c r="L86" s="232"/>
+      <c r="M86" s="232"/>
+      <c r="N86" s="232"/>
+      <c r="O86" s="232"/>
     </row>
     <row r="87" spans="2:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D87" s="229"/>
-      <c r="E87" s="229"/>
-      <c r="F87" s="229"/>
-      <c r="G87" s="229"/>
-      <c r="H87" s="229"/>
-      <c r="I87" s="229"/>
-      <c r="J87" s="229"/>
-      <c r="K87" s="229"/>
-      <c r="L87" s="229"/>
-      <c r="M87" s="229"/>
-      <c r="N87" s="229"/>
-      <c r="O87" s="229"/>
+      <c r="D87" s="232"/>
+      <c r="E87" s="232"/>
+      <c r="F87" s="232"/>
+      <c r="G87" s="232"/>
+      <c r="H87" s="232"/>
+      <c r="I87" s="232"/>
+      <c r="J87" s="232"/>
+      <c r="K87" s="232"/>
+      <c r="L87" s="232"/>
+      <c r="M87" s="232"/>
+      <c r="N87" s="232"/>
+      <c r="O87" s="232"/>
     </row>
     <row r="88" spans="2:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D88" s="229"/>
-      <c r="E88" s="229"/>
-      <c r="F88" s="229"/>
-      <c r="G88" s="229"/>
-      <c r="H88" s="229"/>
-      <c r="I88" s="229"/>
-      <c r="J88" s="229"/>
-      <c r="K88" s="229"/>
-      <c r="L88" s="229"/>
-      <c r="M88" s="229"/>
-      <c r="N88" s="229"/>
-      <c r="O88" s="229"/>
+      <c r="D88" s="232"/>
+      <c r="E88" s="232"/>
+      <c r="F88" s="232"/>
+      <c r="G88" s="232"/>
+      <c r="H88" s="232"/>
+      <c r="I88" s="232"/>
+      <c r="J88" s="232"/>
+      <c r="K88" s="232"/>
+      <c r="L88" s="232"/>
+      <c r="M88" s="232"/>
+      <c r="N88" s="232"/>
+      <c r="O88" s="232"/>
     </row>
     <row r="89" spans="2:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D89" s="229"/>
-      <c r="E89" s="229"/>
-      <c r="F89" s="229"/>
-      <c r="G89" s="229"/>
-      <c r="H89" s="229"/>
-      <c r="I89" s="229"/>
-      <c r="J89" s="229"/>
-      <c r="K89" s="229"/>
-      <c r="L89" s="229"/>
-      <c r="M89" s="229"/>
-      <c r="N89" s="229"/>
-      <c r="O89" s="229"/>
+      <c r="D89" s="232"/>
+      <c r="E89" s="232"/>
+      <c r="F89" s="232"/>
+      <c r="G89" s="232"/>
+      <c r="H89" s="232"/>
+      <c r="I89" s="232"/>
+      <c r="J89" s="232"/>
+      <c r="K89" s="232"/>
+      <c r="L89" s="232"/>
+      <c r="M89" s="232"/>
+      <c r="N89" s="232"/>
+      <c r="O89" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="D84:O89"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
@@ -17201,13 +17208,6 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -17225,32 +17225,32 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="269" t="s">
+      <c r="A2" s="272" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="251" t="s">
+      <c r="D2" s="249" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="269" t="s">
+      <c r="E2" s="272" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="271" t="s">
+      <c r="F2" s="274" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="270"/>
-      <c r="B3" s="252"/>
-      <c r="C3" s="252"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="270"/>
-      <c r="F3" s="272"/>
+      <c r="A3" s="273"/>
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="250"/>
+      <c r="E3" s="273"/>
+      <c r="F3" s="275"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="89" t="s">
@@ -18781,28 +18781,28 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="278"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="290"/>
       <c r="I3" s="68"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
       <c r="L4" s="82"/>
@@ -18922,45 +18922,45 @@
       <c r="J15" s="81"/>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="279">
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278">
         <f>PRORRATEO!M8</f>
         <v>217600.01</v>
       </c>
-      <c r="H16" s="280"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="70"/>
       <c r="J16" s="80"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="276" t="s">
+      <c r="B20" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="278"/>
+      <c r="C20" s="289"/>
+      <c r="D20" s="289"/>
+      <c r="E20" s="289"/>
+      <c r="F20" s="289"/>
+      <c r="G20" s="289"/>
+      <c r="H20" s="290"/>
       <c r="I20" s="68"/>
       <c r="J20" s="69"/>
     </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="273" t="s">
+      <c r="B21" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="274"/>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="275"/>
+      <c r="C21" s="281"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="281"/>
+      <c r="H21" s="282"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
     </row>
@@ -19078,46 +19078,46 @@
       <c r="J32" s="81"/>
     </row>
     <row r="33" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="281" t="s">
+      <c r="B33" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="282"/>
-      <c r="D33" s="282"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="282"/>
-      <c r="G33" s="279">
+      <c r="C33" s="277"/>
+      <c r="D33" s="277"/>
+      <c r="E33" s="277"/>
+      <c r="F33" s="277"/>
+      <c r="G33" s="278">
         <f>PRORRATEO!M9</f>
         <v>158078.01999999999</v>
       </c>
-      <c r="H33" s="280"/>
+      <c r="H33" s="279"/>
       <c r="I33" s="70"/>
       <c r="J33" s="80"/>
     </row>
     <row r="36" spans="2:10" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:10" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="276" t="s">
+      <c r="B38" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="277"/>
-      <c r="D38" s="277"/>
-      <c r="E38" s="277"/>
-      <c r="F38" s="277"/>
-      <c r="G38" s="277"/>
-      <c r="H38" s="278"/>
+      <c r="C38" s="289"/>
+      <c r="D38" s="289"/>
+      <c r="E38" s="289"/>
+      <c r="F38" s="289"/>
+      <c r="G38" s="289"/>
+      <c r="H38" s="290"/>
       <c r="I38" s="68"/>
       <c r="J38" s="69"/>
     </row>
     <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="273" t="s">
+      <c r="B39" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="274"/>
-      <c r="D39" s="274"/>
-      <c r="E39" s="274"/>
-      <c r="F39" s="274"/>
-      <c r="G39" s="274"/>
-      <c r="H39" s="275"/>
+      <c r="C39" s="281"/>
+      <c r="D39" s="281"/>
+      <c r="E39" s="281"/>
+      <c r="F39" s="281"/>
+      <c r="G39" s="281"/>
+      <c r="H39" s="282"/>
       <c r="I39" s="1"/>
       <c r="J39" s="2"/>
     </row>
@@ -19235,45 +19235,45 @@
       <c r="J50" s="81"/>
     </row>
     <row r="51" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="281" t="s">
+      <c r="B51" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="279">
+      <c r="C51" s="277"/>
+      <c r="D51" s="277"/>
+      <c r="E51" s="277"/>
+      <c r="F51" s="277"/>
+      <c r="G51" s="278">
         <f>PRORRATEO!M10</f>
         <v>179200.03</v>
       </c>
-      <c r="H51" s="280"/>
+      <c r="H51" s="279"/>
       <c r="I51" s="70"/>
       <c r="J51" s="80"/>
     </row>
     <row r="54" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="276" t="s">
+      <c r="B55" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C55" s="277"/>
-      <c r="D55" s="277"/>
-      <c r="E55" s="277"/>
-      <c r="F55" s="277"/>
-      <c r="G55" s="277"/>
-      <c r="H55" s="278"/>
+      <c r="C55" s="289"/>
+      <c r="D55" s="289"/>
+      <c r="E55" s="289"/>
+      <c r="F55" s="289"/>
+      <c r="G55" s="289"/>
+      <c r="H55" s="290"/>
       <c r="I55" s="68"/>
       <c r="J55" s="69"/>
     </row>
     <row r="56" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="273" t="s">
+      <c r="B56" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="274"/>
-      <c r="D56" s="274"/>
-      <c r="E56" s="274"/>
-      <c r="F56" s="274"/>
-      <c r="G56" s="274"/>
-      <c r="H56" s="275"/>
+      <c r="C56" s="281"/>
+      <c r="D56" s="281"/>
+      <c r="E56" s="281"/>
+      <c r="F56" s="281"/>
+      <c r="G56" s="281"/>
+      <c r="H56" s="282"/>
       <c r="I56" s="1"/>
       <c r="J56" s="2"/>
     </row>
@@ -19391,18 +19391,18 @@
       <c r="J67" s="81"/>
     </row>
     <row r="68" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="281" t="s">
+      <c r="B68" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C68" s="282"/>
-      <c r="D68" s="282"/>
-      <c r="E68" s="282"/>
-      <c r="F68" s="282"/>
-      <c r="G68" s="279">
+      <c r="C68" s="277"/>
+      <c r="D68" s="277"/>
+      <c r="E68" s="277"/>
+      <c r="F68" s="277"/>
+      <c r="G68" s="278">
         <f>PRORRATEO!M11</f>
         <v>83887.039999999994</v>
       </c>
-      <c r="H68" s="280"/>
+      <c r="H68" s="279"/>
       <c r="I68" s="70"/>
       <c r="J68" s="80"/>
     </row>
@@ -19410,28 +19410,28 @@
     <row r="71" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="73" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="276" t="s">
+      <c r="B73" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C73" s="277"/>
-      <c r="D73" s="277"/>
-      <c r="E73" s="277"/>
-      <c r="F73" s="277"/>
-      <c r="G73" s="277"/>
-      <c r="H73" s="278"/>
+      <c r="C73" s="289"/>
+      <c r="D73" s="289"/>
+      <c r="E73" s="289"/>
+      <c r="F73" s="289"/>
+      <c r="G73" s="289"/>
+      <c r="H73" s="290"/>
       <c r="I73" s="68"/>
       <c r="J73" s="69"/>
     </row>
     <row r="74" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="273" t="s">
+      <c r="B74" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="274"/>
-      <c r="D74" s="274"/>
-      <c r="E74" s="274"/>
-      <c r="F74" s="274"/>
-      <c r="G74" s="274"/>
-      <c r="H74" s="275"/>
+      <c r="C74" s="281"/>
+      <c r="D74" s="281"/>
+      <c r="E74" s="281"/>
+      <c r="F74" s="281"/>
+      <c r="G74" s="281"/>
+      <c r="H74" s="282"/>
       <c r="I74" s="1"/>
       <c r="J74" s="2"/>
     </row>
@@ -19549,18 +19549,18 @@
       <c r="J85" s="81"/>
     </row>
     <row r="86" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="281" t="s">
+      <c r="B86" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C86" s="282"/>
-      <c r="D86" s="282"/>
-      <c r="E86" s="282"/>
-      <c r="F86" s="282"/>
-      <c r="G86" s="279">
+      <c r="C86" s="277"/>
+      <c r="D86" s="277"/>
+      <c r="E86" s="277"/>
+      <c r="F86" s="277"/>
+      <c r="G86" s="278">
         <f>PRORRATEO!M12</f>
         <v>89600.05</v>
       </c>
-      <c r="H86" s="280"/>
+      <c r="H86" s="279"/>
       <c r="I86" s="70"/>
       <c r="J86" s="80"/>
     </row>
@@ -19569,28 +19569,28 @@
     <row r="89" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="276" t="s">
+      <c r="B91" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C91" s="277"/>
-      <c r="D91" s="277"/>
-      <c r="E91" s="277"/>
-      <c r="F91" s="277"/>
-      <c r="G91" s="277"/>
-      <c r="H91" s="278"/>
+      <c r="C91" s="289"/>
+      <c r="D91" s="289"/>
+      <c r="E91" s="289"/>
+      <c r="F91" s="289"/>
+      <c r="G91" s="289"/>
+      <c r="H91" s="290"/>
       <c r="I91" s="68"/>
       <c r="J91" s="69"/>
     </row>
     <row r="92" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="273" t="s">
+      <c r="B92" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="274"/>
-      <c r="D92" s="274"/>
-      <c r="E92" s="274"/>
-      <c r="F92" s="274"/>
-      <c r="G92" s="274"/>
-      <c r="H92" s="275"/>
+      <c r="C92" s="281"/>
+      <c r="D92" s="281"/>
+      <c r="E92" s="281"/>
+      <c r="F92" s="281"/>
+      <c r="G92" s="281"/>
+      <c r="H92" s="282"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
     </row>
@@ -19708,23 +19708,52 @@
       <c r="J103" s="81"/>
     </row>
     <row r="104" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="281" t="s">
+      <c r="B104" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="282"/>
-      <c r="D104" s="282"/>
-      <c r="E104" s="282"/>
-      <c r="F104" s="282"/>
-      <c r="G104" s="279">
+      <c r="C104" s="277"/>
+      <c r="D104" s="277"/>
+      <c r="E104" s="277"/>
+      <c r="F104" s="277"/>
+      <c r="G104" s="278">
         <f>PRORRATEO!M13</f>
         <v>89600.06</v>
       </c>
-      <c r="H104" s="280"/>
+      <c r="H104" s="279"/>
       <c r="I104" s="70"/>
       <c r="J104" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="G68:H68"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="G104:H104"/>
     <mergeCell ref="B74:H74"/>
@@ -19738,35 +19767,6 @@
     <mergeCell ref="B96:H96"/>
     <mergeCell ref="I98:J98"/>
     <mergeCell ref="I100:J100"/>
-    <mergeCell ref="B73:H73"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B8:H8"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19787,28 +19787,28 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="278"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="290"/>
       <c r="I3" s="68"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
     </row>
@@ -19926,45 +19926,45 @@
       <c r="J15" s="81"/>
     </row>
     <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="279">
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278">
         <f>PRORRATEO!M14</f>
         <v>1766465.07</v>
       </c>
-      <c r="H16" s="280"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="70"/>
       <c r="J16" s="80"/>
     </row>
     <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="276" t="s">
+      <c r="B20" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="278"/>
+      <c r="C20" s="289"/>
+      <c r="D20" s="289"/>
+      <c r="E20" s="289"/>
+      <c r="F20" s="289"/>
+      <c r="G20" s="289"/>
+      <c r="H20" s="290"/>
       <c r="I20" s="68"/>
       <c r="J20" s="69"/>
     </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="273" t="s">
+      <c r="B21" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="274"/>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="275"/>
+      <c r="C21" s="281"/>
+      <c r="D21" s="281"/>
+      <c r="E21" s="281"/>
+      <c r="F21" s="281"/>
+      <c r="G21" s="281"/>
+      <c r="H21" s="282"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
     </row>
@@ -20082,46 +20082,46 @@
       <c r="J32" s="81"/>
     </row>
     <row r="33" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="281" t="s">
+      <c r="B33" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="282"/>
-      <c r="D33" s="282"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="282"/>
-      <c r="G33" s="279">
+      <c r="C33" s="277"/>
+      <c r="D33" s="277"/>
+      <c r="E33" s="277"/>
+      <c r="F33" s="277"/>
+      <c r="G33" s="278">
         <f>PRORRATEO!M15</f>
         <v>102400.08</v>
       </c>
-      <c r="H33" s="280"/>
+      <c r="H33" s="279"/>
       <c r="I33" s="70"/>
       <c r="J33" s="80"/>
     </row>
     <row r="35" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="276" t="s">
+      <c r="B37" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="277"/>
-      <c r="D37" s="277"/>
-      <c r="E37" s="277"/>
-      <c r="F37" s="277"/>
-      <c r="G37" s="277"/>
-      <c r="H37" s="278"/>
+      <c r="C37" s="289"/>
+      <c r="D37" s="289"/>
+      <c r="E37" s="289"/>
+      <c r="F37" s="289"/>
+      <c r="G37" s="289"/>
+      <c r="H37" s="290"/>
       <c r="I37" s="68"/>
       <c r="J37" s="69"/>
     </row>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="273" t="s">
+      <c r="B38" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="274"/>
-      <c r="D38" s="274"/>
-      <c r="E38" s="274"/>
-      <c r="F38" s="274"/>
-      <c r="G38" s="274"/>
-      <c r="H38" s="275"/>
+      <c r="C38" s="281"/>
+      <c r="D38" s="281"/>
+      <c r="E38" s="281"/>
+      <c r="F38" s="281"/>
+      <c r="G38" s="281"/>
+      <c r="H38" s="282"/>
       <c r="I38" s="1"/>
       <c r="J38" s="2"/>
     </row>
@@ -20239,45 +20239,45 @@
       <c r="J49" s="81"/>
     </row>
     <row r="50" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="281" t="s">
+      <c r="B50" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="282"/>
-      <c r="D50" s="282"/>
-      <c r="E50" s="282"/>
-      <c r="F50" s="282"/>
-      <c r="G50" s="279">
+      <c r="C50" s="277"/>
+      <c r="D50" s="277"/>
+      <c r="E50" s="277"/>
+      <c r="F50" s="277"/>
+      <c r="G50" s="278">
         <f>PRORRATEO!M16</f>
         <v>1624873.09</v>
       </c>
-      <c r="H50" s="280"/>
+      <c r="H50" s="279"/>
       <c r="I50" s="70"/>
       <c r="J50" s="80"/>
     </row>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="54" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="276" t="s">
+      <c r="B54" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C54" s="277"/>
-      <c r="D54" s="277"/>
-      <c r="E54" s="277"/>
-      <c r="F54" s="277"/>
-      <c r="G54" s="277"/>
-      <c r="H54" s="278"/>
+      <c r="C54" s="289"/>
+      <c r="D54" s="289"/>
+      <c r="E54" s="289"/>
+      <c r="F54" s="289"/>
+      <c r="G54" s="289"/>
+      <c r="H54" s="290"/>
       <c r="I54" s="68"/>
       <c r="J54" s="69"/>
     </row>
     <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="273" t="s">
+      <c r="B55" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="274"/>
-      <c r="D55" s="274"/>
-      <c r="E55" s="274"/>
-      <c r="F55" s="274"/>
-      <c r="G55" s="274"/>
-      <c r="H55" s="275"/>
+      <c r="C55" s="281"/>
+      <c r="D55" s="281"/>
+      <c r="E55" s="281"/>
+      <c r="F55" s="281"/>
+      <c r="G55" s="281"/>
+      <c r="H55" s="282"/>
       <c r="I55" s="1"/>
       <c r="J55" s="2"/>
     </row>
@@ -20395,45 +20395,45 @@
       <c r="J66" s="81"/>
     </row>
     <row r="67" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="281" t="s">
+      <c r="B67" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="282"/>
-      <c r="D67" s="282"/>
-      <c r="E67" s="282"/>
-      <c r="F67" s="282"/>
-      <c r="G67" s="279">
+      <c r="C67" s="277"/>
+      <c r="D67" s="277"/>
+      <c r="E67" s="277"/>
+      <c r="F67" s="277"/>
+      <c r="G67" s="278">
         <f>PRORRATEO!M17</f>
         <v>89600.1</v>
       </c>
-      <c r="H67" s="280"/>
+      <c r="H67" s="279"/>
       <c r="I67" s="70"/>
       <c r="J67" s="80"/>
     </row>
     <row r="71" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="72" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="276" t="s">
+      <c r="B72" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C72" s="277"/>
-      <c r="D72" s="277"/>
-      <c r="E72" s="277"/>
-      <c r="F72" s="277"/>
-      <c r="G72" s="277"/>
-      <c r="H72" s="278"/>
+      <c r="C72" s="289"/>
+      <c r="D72" s="289"/>
+      <c r="E72" s="289"/>
+      <c r="F72" s="289"/>
+      <c r="G72" s="289"/>
+      <c r="H72" s="290"/>
       <c r="I72" s="68"/>
       <c r="J72" s="69"/>
     </row>
     <row r="73" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="273" t="s">
+      <c r="B73" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C73" s="274"/>
-      <c r="D73" s="274"/>
-      <c r="E73" s="274"/>
-      <c r="F73" s="274"/>
-      <c r="G73" s="274"/>
-      <c r="H73" s="275"/>
+      <c r="C73" s="281"/>
+      <c r="D73" s="281"/>
+      <c r="E73" s="281"/>
+      <c r="F73" s="281"/>
+      <c r="G73" s="281"/>
+      <c r="H73" s="282"/>
       <c r="I73" s="1"/>
       <c r="J73" s="2"/>
     </row>
@@ -20551,45 +20551,45 @@
       <c r="J84" s="81"/>
     </row>
     <row r="85" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="281" t="s">
+      <c r="B85" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C85" s="282"/>
-      <c r="D85" s="282"/>
-      <c r="E85" s="282"/>
-      <c r="F85" s="282"/>
-      <c r="G85" s="279">
+      <c r="C85" s="277"/>
+      <c r="D85" s="277"/>
+      <c r="E85" s="277"/>
+      <c r="F85" s="277"/>
+      <c r="G85" s="278">
         <f>PRORRATEO!M18</f>
         <v>89600.11</v>
       </c>
-      <c r="H85" s="280"/>
+      <c r="H85" s="279"/>
       <c r="I85" s="70"/>
       <c r="J85" s="80"/>
     </row>
     <row r="89" spans="2:10" ht="183" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="276" t="s">
+      <c r="B90" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C90" s="277"/>
-      <c r="D90" s="277"/>
-      <c r="E90" s="277"/>
-      <c r="F90" s="277"/>
-      <c r="G90" s="277"/>
-      <c r="H90" s="278"/>
+      <c r="C90" s="289"/>
+      <c r="D90" s="289"/>
+      <c r="E90" s="289"/>
+      <c r="F90" s="289"/>
+      <c r="G90" s="289"/>
+      <c r="H90" s="290"/>
       <c r="I90" s="68"/>
       <c r="J90" s="69"/>
     </row>
     <row r="91" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="273" t="s">
+      <c r="B91" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C91" s="274"/>
-      <c r="D91" s="274"/>
-      <c r="E91" s="274"/>
-      <c r="F91" s="274"/>
-      <c r="G91" s="274"/>
-      <c r="H91" s="275"/>
+      <c r="C91" s="281"/>
+      <c r="D91" s="281"/>
+      <c r="E91" s="281"/>
+      <c r="F91" s="281"/>
+      <c r="G91" s="281"/>
+      <c r="H91" s="282"/>
       <c r="I91" s="1"/>
       <c r="J91" s="2"/>
     </row>
@@ -20707,42 +20707,30 @@
       <c r="J102" s="81"/>
     </row>
     <row r="103" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="281" t="s">
+      <c r="B103" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C103" s="282"/>
-      <c r="D103" s="282"/>
-      <c r="E103" s="282"/>
-      <c r="F103" s="282"/>
-      <c r="G103" s="279">
+      <c r="C103" s="277"/>
+      <c r="D103" s="277"/>
+      <c r="E103" s="277"/>
+      <c r="F103" s="277"/>
+      <c r="G103" s="278">
         <f>PRORRATEO!M19</f>
         <v>89600.12</v>
       </c>
-      <c r="H103" s="280"/>
+      <c r="H103" s="279"/>
       <c r="I103" s="70"/>
       <c r="J103" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="B72:H72"/>
-    <mergeCell ref="B73:H73"/>
-    <mergeCell ref="B77:H77"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B95:H95"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B8:H8"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="G67:H67"/>
     <mergeCell ref="B16:F16"/>
@@ -20759,13 +20747,25 @@
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B77:H77"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="I79:J79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20787,28 +20787,28 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="278"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="290"/>
       <c r="I3" s="68"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
     </row>
@@ -20926,45 +20926,45 @@
       <c r="J15" s="81"/>
     </row>
     <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="279">
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278">
         <f>PRORRATEO!M20</f>
         <v>1332754.1299999999</v>
       </c>
-      <c r="H16" s="280"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="70"/>
       <c r="J16" s="80"/>
     </row>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="276" t="s">
+      <c r="B21" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
-      <c r="E21" s="277"/>
-      <c r="F21" s="277"/>
-      <c r="G21" s="277"/>
-      <c r="H21" s="278"/>
+      <c r="C21" s="289"/>
+      <c r="D21" s="289"/>
+      <c r="E21" s="289"/>
+      <c r="F21" s="289"/>
+      <c r="G21" s="289"/>
+      <c r="H21" s="290"/>
       <c r="I21" s="68"/>
       <c r="J21" s="69"/>
     </row>
     <row r="22" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="273" t="s">
+      <c r="B22" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="274"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="275"/>
+      <c r="C22" s="281"/>
+      <c r="D22" s="281"/>
+      <c r="E22" s="281"/>
+      <c r="F22" s="281"/>
+      <c r="G22" s="281"/>
+      <c r="H22" s="282"/>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
     </row>
@@ -21082,18 +21082,18 @@
       <c r="J33" s="81"/>
     </row>
     <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="281" t="s">
+      <c r="B34" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="282"/>
-      <c r="D34" s="282"/>
-      <c r="E34" s="282"/>
-      <c r="F34" s="282"/>
-      <c r="G34" s="279">
+      <c r="C34" s="277"/>
+      <c r="D34" s="277"/>
+      <c r="E34" s="277"/>
+      <c r="F34" s="277"/>
+      <c r="G34" s="278">
         <f>PRORRATEO!M21</f>
         <v>1161292.1399999999</v>
       </c>
-      <c r="H34" s="280"/>
+      <c r="H34" s="279"/>
       <c r="I34" s="70"/>
       <c r="J34" s="80"/>
     </row>
@@ -21102,28 +21102,28 @@
     <row r="37" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="276" t="s">
+      <c r="B39" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="277"/>
-      <c r="D39" s="277"/>
-      <c r="E39" s="277"/>
-      <c r="F39" s="277"/>
-      <c r="G39" s="277"/>
-      <c r="H39" s="278"/>
+      <c r="C39" s="289"/>
+      <c r="D39" s="289"/>
+      <c r="E39" s="289"/>
+      <c r="F39" s="289"/>
+      <c r="G39" s="289"/>
+      <c r="H39" s="290"/>
       <c r="I39" s="68"/>
       <c r="J39" s="69"/>
     </row>
     <row r="40" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="273" t="s">
+      <c r="B40" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="274"/>
-      <c r="D40" s="274"/>
-      <c r="E40" s="274"/>
-      <c r="F40" s="274"/>
-      <c r="G40" s="274"/>
-      <c r="H40" s="275"/>
+      <c r="C40" s="281"/>
+      <c r="D40" s="281"/>
+      <c r="E40" s="281"/>
+      <c r="F40" s="281"/>
+      <c r="G40" s="281"/>
+      <c r="H40" s="282"/>
       <c r="I40" s="1"/>
       <c r="J40" s="2"/>
     </row>
@@ -21241,45 +21241,45 @@
       <c r="J51" s="81"/>
     </row>
     <row r="52" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="281" t="s">
+      <c r="B52" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="282"/>
-      <c r="D52" s="282"/>
-      <c r="E52" s="282"/>
-      <c r="F52" s="282"/>
-      <c r="G52" s="279">
+      <c r="C52" s="277"/>
+      <c r="D52" s="277"/>
+      <c r="E52" s="277"/>
+      <c r="F52" s="277"/>
+      <c r="G52" s="278">
         <f>PRORRATEO!M22</f>
         <v>186200.15</v>
       </c>
-      <c r="H52" s="280"/>
+      <c r="H52" s="279"/>
       <c r="I52" s="70"/>
       <c r="J52" s="80"/>
     </row>
     <row r="56" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="276" t="s">
+      <c r="B57" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="277"/>
-      <c r="D57" s="277"/>
-      <c r="E57" s="277"/>
-      <c r="F57" s="277"/>
-      <c r="G57" s="277"/>
-      <c r="H57" s="278"/>
+      <c r="C57" s="289"/>
+      <c r="D57" s="289"/>
+      <c r="E57" s="289"/>
+      <c r="F57" s="289"/>
+      <c r="G57" s="289"/>
+      <c r="H57" s="290"/>
       <c r="I57" s="68"/>
       <c r="J57" s="69"/>
     </row>
     <row r="58" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="273" t="s">
+      <c r="B58" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="274"/>
-      <c r="D58" s="274"/>
-      <c r="E58" s="274"/>
-      <c r="F58" s="274"/>
-      <c r="G58" s="274"/>
-      <c r="H58" s="275"/>
+      <c r="C58" s="281"/>
+      <c r="D58" s="281"/>
+      <c r="E58" s="281"/>
+      <c r="F58" s="281"/>
+      <c r="G58" s="281"/>
+      <c r="H58" s="282"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
     </row>
@@ -21397,45 +21397,45 @@
       <c r="J69" s="81"/>
     </row>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="281" t="s">
+      <c r="B70" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="282"/>
-      <c r="D70" s="282"/>
-      <c r="E70" s="282"/>
-      <c r="F70" s="282"/>
-      <c r="G70" s="279">
+      <c r="C70" s="277"/>
+      <c r="D70" s="277"/>
+      <c r="E70" s="277"/>
+      <c r="F70" s="277"/>
+      <c r="G70" s="278">
         <f>PRORRATEO!M23</f>
         <v>80859.16</v>
       </c>
-      <c r="H70" s="280"/>
+      <c r="H70" s="279"/>
       <c r="I70" s="70"/>
       <c r="J70" s="80"/>
     </row>
     <row r="74" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="276" t="s">
+      <c r="B75" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C75" s="277"/>
-      <c r="D75" s="277"/>
-      <c r="E75" s="277"/>
-      <c r="F75" s="277"/>
-      <c r="G75" s="277"/>
-      <c r="H75" s="278"/>
+      <c r="C75" s="289"/>
+      <c r="D75" s="289"/>
+      <c r="E75" s="289"/>
+      <c r="F75" s="289"/>
+      <c r="G75" s="289"/>
+      <c r="H75" s="290"/>
       <c r="I75" s="68"/>
       <c r="J75" s="69"/>
     </row>
     <row r="76" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="273" t="s">
+      <c r="B76" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="274"/>
-      <c r="D76" s="274"/>
-      <c r="E76" s="274"/>
-      <c r="F76" s="274"/>
-      <c r="G76" s="274"/>
-      <c r="H76" s="275"/>
+      <c r="C76" s="281"/>
+      <c r="D76" s="281"/>
+      <c r="E76" s="281"/>
+      <c r="F76" s="281"/>
+      <c r="G76" s="281"/>
+      <c r="H76" s="282"/>
       <c r="I76" s="1"/>
       <c r="J76" s="2"/>
     </row>
@@ -21553,45 +21553,45 @@
       <c r="J87" s="81"/>
     </row>
     <row r="88" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="281" t="s">
+      <c r="B88" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C88" s="282"/>
-      <c r="D88" s="282"/>
-      <c r="E88" s="282"/>
-      <c r="F88" s="282"/>
-      <c r="G88" s="279">
+      <c r="C88" s="277"/>
+      <c r="D88" s="277"/>
+      <c r="E88" s="277"/>
+      <c r="F88" s="277"/>
+      <c r="G88" s="278">
         <f>PRORRATEO!M24</f>
         <v>1522148.17</v>
       </c>
-      <c r="H88" s="280"/>
+      <c r="H88" s="279"/>
       <c r="I88" s="70"/>
       <c r="J88" s="80"/>
     </row>
     <row r="92" spans="2:10" ht="169.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="93" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="276" t="s">
+      <c r="B93" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C93" s="277"/>
-      <c r="D93" s="277"/>
-      <c r="E93" s="277"/>
-      <c r="F93" s="277"/>
-      <c r="G93" s="277"/>
-      <c r="H93" s="278"/>
+      <c r="C93" s="289"/>
+      <c r="D93" s="289"/>
+      <c r="E93" s="289"/>
+      <c r="F93" s="289"/>
+      <c r="G93" s="289"/>
+      <c r="H93" s="290"/>
       <c r="I93" s="68"/>
       <c r="J93" s="69"/>
     </row>
     <row r="94" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="273" t="s">
+      <c r="B94" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C94" s="274"/>
-      <c r="D94" s="274"/>
-      <c r="E94" s="274"/>
-      <c r="F94" s="274"/>
-      <c r="G94" s="274"/>
-      <c r="H94" s="275"/>
+      <c r="C94" s="281"/>
+      <c r="D94" s="281"/>
+      <c r="E94" s="281"/>
+      <c r="F94" s="281"/>
+      <c r="G94" s="281"/>
+      <c r="H94" s="282"/>
       <c r="I94" s="1"/>
       <c r="J94" s="2"/>
     </row>
@@ -21709,42 +21709,30 @@
       <c r="J105" s="81"/>
     </row>
     <row r="106" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="281" t="s">
+      <c r="B106" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="282"/>
-      <c r="D106" s="282"/>
-      <c r="E106" s="282"/>
-      <c r="F106" s="282"/>
-      <c r="G106" s="279">
+      <c r="C106" s="277"/>
+      <c r="D106" s="277"/>
+      <c r="E106" s="277"/>
+      <c r="F106" s="277"/>
+      <c r="G106" s="278">
         <f>PRORRATEO!M25</f>
         <v>5600.18</v>
       </c>
-      <c r="H106" s="280"/>
+      <c r="H106" s="279"/>
       <c r="I106" s="70"/>
       <c r="J106" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B80:H80"/>
-    <mergeCell ref="B93:H93"/>
-    <mergeCell ref="B94:H94"/>
-    <mergeCell ref="B98:H98"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B8:H8"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="G70:H70"/>
     <mergeCell ref="B16:F16"/>
@@ -21761,13 +21749,25 @@
     <mergeCell ref="B44:H44"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I82:J82"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21789,28 +21789,28 @@
   <sheetData>
     <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="278"/>
+      <c r="C3" s="289"/>
+      <c r="D3" s="289"/>
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="290"/>
       <c r="I3" s="68"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="273" t="s">
+      <c r="B4" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2"/>
     </row>
@@ -21928,45 +21928,45 @@
       <c r="J15" s="81"/>
     </row>
     <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="281" t="s">
+      <c r="B16" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="279">
+      <c r="C16" s="277"/>
+      <c r="D16" s="277"/>
+      <c r="E16" s="277"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278">
         <f>PRORRATEO!M26</f>
         <v>393905.19</v>
       </c>
-      <c r="H16" s="280"/>
+      <c r="H16" s="279"/>
       <c r="I16" s="70"/>
       <c r="J16" s="80"/>
     </row>
     <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="276" t="s">
+      <c r="B21" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
-      <c r="E21" s="277"/>
-      <c r="F21" s="277"/>
-      <c r="G21" s="277"/>
-      <c r="H21" s="278"/>
+      <c r="C21" s="289"/>
+      <c r="D21" s="289"/>
+      <c r="E21" s="289"/>
+      <c r="F21" s="289"/>
+      <c r="G21" s="289"/>
+      <c r="H21" s="290"/>
       <c r="I21" s="68"/>
       <c r="J21" s="69"/>
     </row>
     <row r="22" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="273" t="s">
+      <c r="B22" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="274"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="275"/>
+      <c r="C22" s="281"/>
+      <c r="D22" s="281"/>
+      <c r="E22" s="281"/>
+      <c r="F22" s="281"/>
+      <c r="G22" s="281"/>
+      <c r="H22" s="282"/>
       <c r="I22" s="1"/>
       <c r="J22" s="2"/>
     </row>
@@ -22084,18 +22084,18 @@
       <c r="J33" s="81"/>
     </row>
     <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="281" t="s">
+      <c r="B34" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="282"/>
-      <c r="D34" s="282"/>
-      <c r="E34" s="282"/>
-      <c r="F34" s="282"/>
-      <c r="G34" s="279">
+      <c r="C34" s="277"/>
+      <c r="D34" s="277"/>
+      <c r="E34" s="277"/>
+      <c r="F34" s="277"/>
+      <c r="G34" s="278">
         <f>PRORRATEO!M27</f>
         <v>89600.2</v>
       </c>
-      <c r="H34" s="280"/>
+      <c r="H34" s="279"/>
       <c r="I34" s="70"/>
       <c r="J34" s="80"/>
     </row>
@@ -22103,28 +22103,28 @@
     <row r="36" spans="2:10" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:10" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="276" t="s">
+      <c r="B38" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="277"/>
-      <c r="D38" s="277"/>
-      <c r="E38" s="277"/>
-      <c r="F38" s="277"/>
-      <c r="G38" s="277"/>
-      <c r="H38" s="278"/>
+      <c r="C38" s="289"/>
+      <c r="D38" s="289"/>
+      <c r="E38" s="289"/>
+      <c r="F38" s="289"/>
+      <c r="G38" s="289"/>
+      <c r="H38" s="290"/>
       <c r="I38" s="68"/>
       <c r="J38" s="69"/>
     </row>
     <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="273" t="s">
+      <c r="B39" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="274"/>
-      <c r="D39" s="274"/>
-      <c r="E39" s="274"/>
-      <c r="F39" s="274"/>
-      <c r="G39" s="274"/>
-      <c r="H39" s="275"/>
+      <c r="C39" s="281"/>
+      <c r="D39" s="281"/>
+      <c r="E39" s="281"/>
+      <c r="F39" s="281"/>
+      <c r="G39" s="281"/>
+      <c r="H39" s="282"/>
       <c r="I39" s="1"/>
       <c r="J39" s="2"/>
     </row>
@@ -22242,45 +22242,45 @@
       <c r="J50" s="81"/>
     </row>
     <row r="51" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="281" t="s">
+      <c r="B51" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="279">
+      <c r="C51" s="277"/>
+      <c r="D51" s="277"/>
+      <c r="E51" s="277"/>
+      <c r="F51" s="277"/>
+      <c r="G51" s="278">
         <f>PRORRATEO!M28</f>
         <v>1324849.21</v>
       </c>
-      <c r="H51" s="280"/>
+      <c r="H51" s="279"/>
       <c r="I51" s="70"/>
       <c r="J51" s="80"/>
     </row>
     <row r="56" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="276" t="s">
+      <c r="B57" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="277"/>
-      <c r="D57" s="277"/>
-      <c r="E57" s="277"/>
-      <c r="F57" s="277"/>
-      <c r="G57" s="277"/>
-      <c r="H57" s="278"/>
+      <c r="C57" s="289"/>
+      <c r="D57" s="289"/>
+      <c r="E57" s="289"/>
+      <c r="F57" s="289"/>
+      <c r="G57" s="289"/>
+      <c r="H57" s="290"/>
       <c r="I57" s="68"/>
       <c r="J57" s="69"/>
     </row>
     <row r="58" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="273" t="s">
+      <c r="B58" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="274"/>
-      <c r="D58" s="274"/>
-      <c r="E58" s="274"/>
-      <c r="F58" s="274"/>
-      <c r="G58" s="274"/>
-      <c r="H58" s="275"/>
+      <c r="C58" s="281"/>
+      <c r="D58" s="281"/>
+      <c r="E58" s="281"/>
+      <c r="F58" s="281"/>
+      <c r="G58" s="281"/>
+      <c r="H58" s="282"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
     </row>
@@ -22398,45 +22398,45 @@
       <c r="J69" s="81"/>
     </row>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="281" t="s">
+      <c r="B70" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="282"/>
-      <c r="D70" s="282"/>
-      <c r="E70" s="282"/>
-      <c r="F70" s="282"/>
-      <c r="G70" s="279">
+      <c r="C70" s="277"/>
+      <c r="D70" s="277"/>
+      <c r="E70" s="277"/>
+      <c r="F70" s="277"/>
+      <c r="G70" s="278">
         <f>PRORRATEO!M29</f>
         <v>1810627.22</v>
       </c>
-      <c r="H70" s="280"/>
+      <c r="H70" s="279"/>
       <c r="I70" s="70"/>
       <c r="J70" s="80"/>
     </row>
     <row r="73" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="74" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="276" t="s">
+      <c r="B74" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="277"/>
-      <c r="D74" s="277"/>
-      <c r="E74" s="277"/>
-      <c r="F74" s="277"/>
-      <c r="G74" s="277"/>
-      <c r="H74" s="278"/>
+      <c r="C74" s="289"/>
+      <c r="D74" s="289"/>
+      <c r="E74" s="289"/>
+      <c r="F74" s="289"/>
+      <c r="G74" s="289"/>
+      <c r="H74" s="290"/>
       <c r="I74" s="68"/>
       <c r="J74" s="69"/>
     </row>
     <row r="75" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="273" t="s">
+      <c r="B75" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="274"/>
-      <c r="D75" s="274"/>
-      <c r="E75" s="274"/>
-      <c r="F75" s="274"/>
-      <c r="G75" s="274"/>
-      <c r="H75" s="275"/>
+      <c r="C75" s="281"/>
+      <c r="D75" s="281"/>
+      <c r="E75" s="281"/>
+      <c r="F75" s="281"/>
+      <c r="G75" s="281"/>
+      <c r="H75" s="282"/>
       <c r="I75" s="1"/>
       <c r="J75" s="2"/>
     </row>
@@ -22554,45 +22554,45 @@
       <c r="J86" s="81"/>
     </row>
     <row r="87" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="281" t="s">
+      <c r="B87" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C87" s="282"/>
-      <c r="D87" s="282"/>
-      <c r="E87" s="282"/>
-      <c r="F87" s="282"/>
-      <c r="G87" s="279">
+      <c r="C87" s="277"/>
+      <c r="D87" s="277"/>
+      <c r="E87" s="277"/>
+      <c r="F87" s="277"/>
+      <c r="G87" s="278">
         <f>PRORRATEO!M30</f>
         <v>774328.23</v>
       </c>
-      <c r="H87" s="280"/>
+      <c r="H87" s="279"/>
       <c r="I87" s="70"/>
       <c r="J87" s="80"/>
     </row>
     <row r="90" spans="2:10" ht="213.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="276" t="s">
+      <c r="B91" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C91" s="277"/>
-      <c r="D91" s="277"/>
-      <c r="E91" s="277"/>
-      <c r="F91" s="277"/>
-      <c r="G91" s="277"/>
-      <c r="H91" s="278"/>
+      <c r="C91" s="289"/>
+      <c r="D91" s="289"/>
+      <c r="E91" s="289"/>
+      <c r="F91" s="289"/>
+      <c r="G91" s="289"/>
+      <c r="H91" s="290"/>
       <c r="I91" s="68"/>
       <c r="J91" s="69"/>
     </row>
     <row r="92" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="273" t="s">
+      <c r="B92" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="274"/>
-      <c r="D92" s="274"/>
-      <c r="E92" s="274"/>
-      <c r="F92" s="274"/>
-      <c r="G92" s="274"/>
-      <c r="H92" s="275"/>
+      <c r="C92" s="281"/>
+      <c r="D92" s="281"/>
+      <c r="E92" s="281"/>
+      <c r="F92" s="281"/>
+      <c r="G92" s="281"/>
+      <c r="H92" s="282"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
     </row>
@@ -22710,42 +22710,30 @@
       <c r="J103" s="81"/>
     </row>
     <row r="104" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="281" t="s">
+      <c r="B104" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="282"/>
-      <c r="D104" s="282"/>
-      <c r="E104" s="282"/>
-      <c r="F104" s="282"/>
-      <c r="G104" s="279">
+      <c r="C104" s="277"/>
+      <c r="D104" s="277"/>
+      <c r="E104" s="277"/>
+      <c r="F104" s="277"/>
+      <c r="G104" s="278">
         <f>PRORRATEO!M31</f>
         <v>2605536.2400000002</v>
       </c>
-      <c r="H104" s="280"/>
+      <c r="H104" s="279"/>
       <c r="I104" s="70"/>
       <c r="J104" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="B74:H74"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B92:H92"/>
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B8:H8"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="G70:H70"/>
     <mergeCell ref="B16:F16"/>
@@ -22762,13 +22750,25 @@
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I81:J81"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22790,28 +22790,28 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="276" t="s">
+      <c r="B4" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="277"/>
-      <c r="D4" s="277"/>
-      <c r="E4" s="277"/>
-      <c r="F4" s="277"/>
-      <c r="G4" s="277"/>
-      <c r="H4" s="278"/>
+      <c r="C4" s="289"/>
+      <c r="D4" s="289"/>
+      <c r="E4" s="289"/>
+      <c r="F4" s="289"/>
+      <c r="G4" s="289"/>
+      <c r="H4" s="290"/>
       <c r="I4" s="68"/>
       <c r="J4" s="69"/>
     </row>
     <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="273" t="s">
+      <c r="B5" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="274"/>
-      <c r="D5" s="274"/>
-      <c r="E5" s="274"/>
-      <c r="F5" s="274"/>
-      <c r="G5" s="274"/>
-      <c r="H5" s="275"/>
+      <c r="C5" s="281"/>
+      <c r="D5" s="281"/>
+      <c r="E5" s="281"/>
+      <c r="F5" s="281"/>
+      <c r="G5" s="281"/>
+      <c r="H5" s="282"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2"/>
     </row>
@@ -22929,45 +22929,45 @@
       <c r="J16" s="81"/>
     </row>
     <row r="17" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="281" t="s">
+      <c r="B17" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C17" s="282"/>
-      <c r="D17" s="282"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="282"/>
-      <c r="G17" s="279">
+      <c r="C17" s="277"/>
+      <c r="D17" s="277"/>
+      <c r="E17" s="277"/>
+      <c r="F17" s="277"/>
+      <c r="G17" s="278">
         <f>PRORRATEO!M32</f>
         <v>176000.25</v>
       </c>
-      <c r="H17" s="280"/>
+      <c r="H17" s="279"/>
       <c r="I17" s="70"/>
       <c r="J17" s="80"/>
     </row>
     <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="276" t="s">
+      <c r="B22" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="277"/>
-      <c r="D22" s="277"/>
-      <c r="E22" s="277"/>
-      <c r="F22" s="277"/>
-      <c r="G22" s="277"/>
-      <c r="H22" s="278"/>
+      <c r="C22" s="289"/>
+      <c r="D22" s="289"/>
+      <c r="E22" s="289"/>
+      <c r="F22" s="289"/>
+      <c r="G22" s="289"/>
+      <c r="H22" s="290"/>
       <c r="I22" s="68"/>
       <c r="J22" s="69"/>
     </row>
     <row r="23" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="273" t="s">
+      <c r="B23" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="274"/>
-      <c r="D23" s="274"/>
-      <c r="E23" s="274"/>
-      <c r="F23" s="274"/>
-      <c r="G23" s="274"/>
-      <c r="H23" s="275"/>
+      <c r="C23" s="281"/>
+      <c r="D23" s="281"/>
+      <c r="E23" s="281"/>
+      <c r="F23" s="281"/>
+      <c r="G23" s="281"/>
+      <c r="H23" s="282"/>
       <c r="I23" s="1"/>
       <c r="J23" s="2"/>
     </row>
@@ -23085,46 +23085,46 @@
       <c r="J34" s="81"/>
     </row>
     <row r="35" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="281" t="s">
+      <c r="B35" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="282"/>
-      <c r="D35" s="282"/>
-      <c r="E35" s="282"/>
-      <c r="F35" s="282"/>
-      <c r="G35" s="279">
+      <c r="C35" s="277"/>
+      <c r="D35" s="277"/>
+      <c r="E35" s="277"/>
+      <c r="F35" s="277"/>
+      <c r="G35" s="278">
         <f>PRORRATEO!M33</f>
         <v>2973761.26</v>
       </c>
-      <c r="H35" s="280"/>
+      <c r="H35" s="279"/>
       <c r="I35" s="70"/>
       <c r="J35" s="80"/>
     </row>
     <row r="38" spans="2:10" ht="163.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="2:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="276" t="s">
+      <c r="B40" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C40" s="277"/>
-      <c r="D40" s="277"/>
-      <c r="E40" s="277"/>
-      <c r="F40" s="277"/>
-      <c r="G40" s="277"/>
-      <c r="H40" s="278"/>
+      <c r="C40" s="289"/>
+      <c r="D40" s="289"/>
+      <c r="E40" s="289"/>
+      <c r="F40" s="289"/>
+      <c r="G40" s="289"/>
+      <c r="H40" s="290"/>
       <c r="I40" s="68"/>
       <c r="J40" s="69"/>
     </row>
     <row r="41" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="273" t="s">
+      <c r="B41" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="274"/>
-      <c r="D41" s="274"/>
-      <c r="E41" s="274"/>
-      <c r="F41" s="274"/>
-      <c r="G41" s="274"/>
-      <c r="H41" s="275"/>
+      <c r="C41" s="281"/>
+      <c r="D41" s="281"/>
+      <c r="E41" s="281"/>
+      <c r="F41" s="281"/>
+      <c r="G41" s="281"/>
+      <c r="H41" s="282"/>
       <c r="I41" s="1"/>
       <c r="J41" s="2"/>
     </row>
@@ -23242,45 +23242,45 @@
       <c r="J52" s="81"/>
     </row>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="281" t="s">
+      <c r="B53" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C53" s="282"/>
-      <c r="D53" s="282"/>
-      <c r="E53" s="282"/>
-      <c r="F53" s="282"/>
-      <c r="G53" s="279">
+      <c r="C53" s="277"/>
+      <c r="D53" s="277"/>
+      <c r="E53" s="277"/>
+      <c r="F53" s="277"/>
+      <c r="G53" s="278">
         <f>PRORRATEO!M34</f>
         <v>0</v>
       </c>
-      <c r="H53" s="280"/>
+      <c r="H53" s="279"/>
       <c r="I53" s="70"/>
       <c r="J53" s="80"/>
     </row>
     <row r="56" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="276" t="s">
+      <c r="B57" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="277"/>
-      <c r="D57" s="277"/>
-      <c r="E57" s="277"/>
-      <c r="F57" s="277"/>
-      <c r="G57" s="277"/>
-      <c r="H57" s="278"/>
+      <c r="C57" s="289"/>
+      <c r="D57" s="289"/>
+      <c r="E57" s="289"/>
+      <c r="F57" s="289"/>
+      <c r="G57" s="289"/>
+      <c r="H57" s="290"/>
       <c r="I57" s="68"/>
       <c r="J57" s="69"/>
     </row>
     <row r="58" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="273" t="s">
+      <c r="B58" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="274"/>
-      <c r="D58" s="274"/>
-      <c r="E58" s="274"/>
-      <c r="F58" s="274"/>
-      <c r="G58" s="274"/>
-      <c r="H58" s="275"/>
+      <c r="C58" s="281"/>
+      <c r="D58" s="281"/>
+      <c r="E58" s="281"/>
+      <c r="F58" s="281"/>
+      <c r="G58" s="281"/>
+      <c r="H58" s="282"/>
       <c r="I58" s="1"/>
       <c r="J58" s="2"/>
     </row>
@@ -23398,18 +23398,18 @@
       <c r="J69" s="81"/>
     </row>
     <row r="70" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="281" t="s">
+      <c r="B70" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="282"/>
-      <c r="D70" s="282"/>
-      <c r="E70" s="282"/>
-      <c r="F70" s="282"/>
-      <c r="G70" s="279" t="e">
+      <c r="C70" s="277"/>
+      <c r="D70" s="277"/>
+      <c r="E70" s="277"/>
+      <c r="F70" s="277"/>
+      <c r="G70" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H70" s="280"/>
+      <c r="H70" s="279"/>
       <c r="I70" s="70"/>
       <c r="J70" s="80"/>
     </row>
@@ -23417,28 +23417,28 @@
     <row r="72" spans="2:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="73" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="74" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="276" t="s">
+      <c r="B74" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="277"/>
-      <c r="D74" s="277"/>
-      <c r="E74" s="277"/>
-      <c r="F74" s="277"/>
-      <c r="G74" s="277"/>
-      <c r="H74" s="278"/>
+      <c r="C74" s="289"/>
+      <c r="D74" s="289"/>
+      <c r="E74" s="289"/>
+      <c r="F74" s="289"/>
+      <c r="G74" s="289"/>
+      <c r="H74" s="290"/>
       <c r="I74" s="68"/>
       <c r="J74" s="69"/>
     </row>
     <row r="75" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="273" t="s">
+      <c r="B75" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="274"/>
-      <c r="D75" s="274"/>
-      <c r="E75" s="274"/>
-      <c r="F75" s="274"/>
-      <c r="G75" s="274"/>
-      <c r="H75" s="275"/>
+      <c r="C75" s="281"/>
+      <c r="D75" s="281"/>
+      <c r="E75" s="281"/>
+      <c r="F75" s="281"/>
+      <c r="G75" s="281"/>
+      <c r="H75" s="282"/>
       <c r="I75" s="1"/>
       <c r="J75" s="2"/>
     </row>
@@ -23556,45 +23556,45 @@
       <c r="J86" s="81"/>
     </row>
     <row r="87" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="281" t="s">
+      <c r="B87" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C87" s="282"/>
-      <c r="D87" s="282"/>
-      <c r="E87" s="282"/>
-      <c r="F87" s="282"/>
-      <c r="G87" s="279" t="e">
+      <c r="C87" s="277"/>
+      <c r="D87" s="277"/>
+      <c r="E87" s="277"/>
+      <c r="F87" s="277"/>
+      <c r="G87" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H87" s="280"/>
+      <c r="H87" s="279"/>
       <c r="I87" s="70"/>
       <c r="J87" s="80"/>
     </row>
     <row r="90" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="276" t="s">
+      <c r="B91" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C91" s="277"/>
-      <c r="D91" s="277"/>
-      <c r="E91" s="277"/>
-      <c r="F91" s="277"/>
-      <c r="G91" s="277"/>
-      <c r="H91" s="278"/>
+      <c r="C91" s="289"/>
+      <c r="D91" s="289"/>
+      <c r="E91" s="289"/>
+      <c r="F91" s="289"/>
+      <c r="G91" s="289"/>
+      <c r="H91" s="290"/>
       <c r="I91" s="68"/>
       <c r="J91" s="69"/>
     </row>
     <row r="92" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="273" t="s">
+      <c r="B92" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="274"/>
-      <c r="D92" s="274"/>
-      <c r="E92" s="274"/>
-      <c r="F92" s="274"/>
-      <c r="G92" s="274"/>
-      <c r="H92" s="275"/>
+      <c r="C92" s="281"/>
+      <c r="D92" s="281"/>
+      <c r="E92" s="281"/>
+      <c r="F92" s="281"/>
+      <c r="G92" s="281"/>
+      <c r="H92" s="282"/>
       <c r="I92" s="1"/>
       <c r="J92" s="2"/>
     </row>
@@ -23712,45 +23712,45 @@
       <c r="J103" s="81"/>
     </row>
     <row r="104" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="281" t="s">
+      <c r="B104" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C104" s="282"/>
-      <c r="D104" s="282"/>
-      <c r="E104" s="282"/>
-      <c r="F104" s="282"/>
-      <c r="G104" s="279" t="e">
+      <c r="C104" s="277"/>
+      <c r="D104" s="277"/>
+      <c r="E104" s="277"/>
+      <c r="F104" s="277"/>
+      <c r="G104" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H104" s="280"/>
+      <c r="H104" s="279"/>
       <c r="I104" s="70"/>
       <c r="J104" s="80"/>
     </row>
     <row r="107" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="276" t="s">
+      <c r="B108" s="288" t="s">
         <v>209</v>
       </c>
-      <c r="C108" s="277"/>
-      <c r="D108" s="277"/>
-      <c r="E108" s="277"/>
-      <c r="F108" s="277"/>
-      <c r="G108" s="277"/>
-      <c r="H108" s="278"/>
+      <c r="C108" s="289"/>
+      <c r="D108" s="289"/>
+      <c r="E108" s="289"/>
+      <c r="F108" s="289"/>
+      <c r="G108" s="289"/>
+      <c r="H108" s="290"/>
       <c r="I108" s="68"/>
       <c r="J108" s="69"/>
     </row>
     <row r="109" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="273" t="s">
+      <c r="B109" s="280" t="s">
         <v>120</v>
       </c>
-      <c r="C109" s="274"/>
-      <c r="D109" s="274"/>
-      <c r="E109" s="274"/>
-      <c r="F109" s="274"/>
-      <c r="G109" s="274"/>
-      <c r="H109" s="275"/>
+      <c r="C109" s="281"/>
+      <c r="D109" s="281"/>
+      <c r="E109" s="281"/>
+      <c r="F109" s="281"/>
+      <c r="G109" s="281"/>
+      <c r="H109" s="282"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
     </row>
@@ -23868,56 +23868,23 @@
       <c r="J120" s="81"/>
     </row>
     <row r="121" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="281" t="s">
+      <c r="B121" s="276" t="s">
         <v>210</v>
       </c>
-      <c r="C121" s="282"/>
-      <c r="D121" s="282"/>
-      <c r="E121" s="282"/>
-      <c r="F121" s="282"/>
-      <c r="G121" s="279" t="e">
+      <c r="C121" s="277"/>
+      <c r="D121" s="277"/>
+      <c r="E121" s="277"/>
+      <c r="F121" s="277"/>
+      <c r="G121" s="278" t="e">
         <f>PRORRATEO!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H121" s="280"/>
+      <c r="H121" s="279"/>
       <c r="I121" s="70"/>
       <c r="J121" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="B121:F121"/>
-    <mergeCell ref="G121:H121"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B92:H92"/>
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="B108:H108"/>
-    <mergeCell ref="B109:H109"/>
-    <mergeCell ref="B113:H113"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="B74:H74"/>
-    <mergeCell ref="B75:H75"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B58:H58"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B9:H9"/>
@@ -23934,6 +23901,39 @@
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="B35:F35"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="I117:J117"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B108:H108"/>
+    <mergeCell ref="B109:H109"/>
+    <mergeCell ref="B113:H113"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="G104:H104"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
